--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/250000/Output_9_11.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/250000/Output_9_11.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15416.35924641449</v>
+        <v>27427.45224950567</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9829061.531704543</v>
+        <v>9572936.676005716</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22088418.71322985</v>
+        <v>22123460.63075672</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4211281.677884432</v>
+        <v>4213000.095123127</v>
       </c>
     </row>
     <row r="11">
@@ -8667,28 +8667,28 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>86.19202512970136</v>
+        <v>92.06191329280013</v>
       </c>
       <c r="K11" t="n">
-        <v>77.92847416055847</v>
+        <v>86.72591490550931</v>
       </c>
       <c r="L11" t="n">
-        <v>59.40265617601742</v>
+        <v>70.31665934305323</v>
       </c>
       <c r="M11" t="n">
-        <v>34.10756991068988</v>
+        <v>46.25150133729366</v>
       </c>
       <c r="N11" t="n">
-        <v>29.9990535463397</v>
+        <v>42.33948647951536</v>
       </c>
       <c r="O11" t="n">
-        <v>41.7972164468124</v>
+        <v>53.44993733213093</v>
       </c>
       <c r="P11" t="n">
-        <v>70.52245304170174</v>
+        <v>80.46778072209531</v>
       </c>
       <c r="Q11" t="n">
-        <v>101.6187652513339</v>
+        <v>109.0872921559756</v>
       </c>
       <c r="R11" t="n">
         <v>65.71641987298243</v>
@@ -8746,13 +8746,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J12" t="n">
-        <v>70.34330591194971</v>
+        <v>73.83937108913169</v>
       </c>
       <c r="K12" t="n">
-        <v>41.28364652152882</v>
+        <v>47.25897875440141</v>
       </c>
       <c r="L12" t="n">
-        <v>8.720511855345904</v>
+        <v>16.75508344424118</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -8761,13 +8761,13 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3258104821803158</v>
+        <v>9.130000058643361</v>
       </c>
       <c r="P12" t="n">
-        <v>19.78984137659441</v>
+        <v>26.85597970277001</v>
       </c>
       <c r="Q12" t="n">
-        <v>63.65241559545548</v>
+        <v>68.37594193669796</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8828,22 +8828,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K13" t="n">
-        <v>70.76997948201083</v>
+        <v>74.37427626277801</v>
       </c>
       <c r="L13" t="n">
-        <v>60.35333201894322</v>
+        <v>64.96559098237566</v>
       </c>
       <c r="M13" t="n">
-        <v>60.34293148858869</v>
+        <v>65.20591187910269</v>
       </c>
       <c r="N13" t="n">
-        <v>50.9712165963807</v>
+        <v>55.71856618250388</v>
       </c>
       <c r="O13" t="n">
-        <v>67.59844009118704</v>
+        <v>71.9833858147683</v>
       </c>
       <c r="P13" t="n">
-        <v>77.09665978685257</v>
+        <v>80.84873837615827</v>
       </c>
       <c r="Q13" t="n">
         <v>65.34295837775146</v>
@@ -8904,28 +8904,28 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>86.19202512970136</v>
+        <v>92.06191329280013</v>
       </c>
       <c r="K14" t="n">
-        <v>77.92847416055847</v>
+        <v>86.72591490550931</v>
       </c>
       <c r="L14" t="n">
-        <v>59.40265617601742</v>
+        <v>70.31665934305323</v>
       </c>
       <c r="M14" t="n">
-        <v>34.10756991068988</v>
+        <v>46.25150133729366</v>
       </c>
       <c r="N14" t="n">
-        <v>29.9990535463397</v>
+        <v>42.33948647951536</v>
       </c>
       <c r="O14" t="n">
-        <v>41.7972164468124</v>
+        <v>53.44993733213093</v>
       </c>
       <c r="P14" t="n">
-        <v>70.52245304170174</v>
+        <v>80.46778072209531</v>
       </c>
       <c r="Q14" t="n">
-        <v>101.6187652513339</v>
+        <v>109.0872921559756</v>
       </c>
       <c r="R14" t="n">
         <v>65.71641987298243</v>
@@ -8983,13 +8983,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J15" t="n">
-        <v>70.34330591194971</v>
+        <v>73.83937108913169</v>
       </c>
       <c r="K15" t="n">
-        <v>41.28364652152882</v>
+        <v>47.25897875440141</v>
       </c>
       <c r="L15" t="n">
-        <v>8.720511855345904</v>
+        <v>16.75508344424118</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -8998,13 +8998,13 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.325810482180259</v>
+        <v>9.130000058643361</v>
       </c>
       <c r="P15" t="n">
-        <v>19.78984137659441</v>
+        <v>26.85597970277001</v>
       </c>
       <c r="Q15" t="n">
-        <v>63.65241559545548</v>
+        <v>68.37594193669796</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9065,22 +9065,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K16" t="n">
-        <v>70.76997948201083</v>
+        <v>74.37427626277801</v>
       </c>
       <c r="L16" t="n">
-        <v>60.35333201894322</v>
+        <v>64.96559098237566</v>
       </c>
       <c r="M16" t="n">
-        <v>60.34293148858869</v>
+        <v>65.20591187910269</v>
       </c>
       <c r="N16" t="n">
-        <v>50.9712165963807</v>
+        <v>55.71856618250388</v>
       </c>
       <c r="O16" t="n">
-        <v>67.59844009118704</v>
+        <v>71.9833858147683</v>
       </c>
       <c r="P16" t="n">
-        <v>77.09665978685257</v>
+        <v>80.84873837615827</v>
       </c>
       <c r="Q16" t="n">
         <v>65.34295837775146</v>
@@ -9141,28 +9141,28 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>86.19202512970136</v>
+        <v>92.06191329280011</v>
       </c>
       <c r="K17" t="n">
-        <v>77.92847416055847</v>
+        <v>86.72591490550931</v>
       </c>
       <c r="L17" t="n">
-        <v>59.40265617601742</v>
+        <v>70.31665934305323</v>
       </c>
       <c r="M17" t="n">
-        <v>34.10756991068988</v>
+        <v>46.25150133729363</v>
       </c>
       <c r="N17" t="n">
-        <v>29.9990535463397</v>
+        <v>42.33948647951536</v>
       </c>
       <c r="O17" t="n">
-        <v>41.7972164468124</v>
+        <v>53.44993733213093</v>
       </c>
       <c r="P17" t="n">
-        <v>70.52245304170174</v>
+        <v>80.46778072209531</v>
       </c>
       <c r="Q17" t="n">
-        <v>101.6187652513339</v>
+        <v>109.0872921559756</v>
       </c>
       <c r="R17" t="n">
         <v>65.71641987298243</v>
@@ -9220,13 +9220,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J18" t="n">
-        <v>70.34330591194971</v>
+        <v>73.83937108913167</v>
       </c>
       <c r="K18" t="n">
-        <v>41.28364652152882</v>
+        <v>47.25897875440141</v>
       </c>
       <c r="L18" t="n">
-        <v>8.720511855345904</v>
+        <v>16.75508344424118</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -9235,13 +9235,13 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3258104821803158</v>
+        <v>9.130000058643361</v>
       </c>
       <c r="P18" t="n">
-        <v>19.78984137659441</v>
+        <v>26.85597970277001</v>
       </c>
       <c r="Q18" t="n">
-        <v>63.65241559545548</v>
+        <v>68.37594193669796</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9302,22 +9302,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K19" t="n">
-        <v>70.76997948201083</v>
+        <v>74.37427626277801</v>
       </c>
       <c r="L19" t="n">
-        <v>60.35333201894322</v>
+        <v>64.96559098237566</v>
       </c>
       <c r="M19" t="n">
-        <v>60.34293148858869</v>
+        <v>65.20591187910269</v>
       </c>
       <c r="N19" t="n">
-        <v>50.9712165963807</v>
+        <v>55.71856618250388</v>
       </c>
       <c r="O19" t="n">
-        <v>67.59844009118704</v>
+        <v>71.98338581476828</v>
       </c>
       <c r="P19" t="n">
-        <v>77.09665978685257</v>
+        <v>80.84873837615825</v>
       </c>
       <c r="Q19" t="n">
         <v>65.34295837775146</v>
@@ -9378,28 +9378,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>86.19202512970136</v>
+        <v>92.06191329280013</v>
       </c>
       <c r="K20" t="n">
-        <v>77.92847416055847</v>
+        <v>86.72591490550931</v>
       </c>
       <c r="L20" t="n">
-        <v>59.40265617601742</v>
+        <v>70.31665934305323</v>
       </c>
       <c r="M20" t="n">
-        <v>34.10756991068988</v>
+        <v>46.25150133729366</v>
       </c>
       <c r="N20" t="n">
-        <v>29.9990535463397</v>
+        <v>42.33948647951536</v>
       </c>
       <c r="O20" t="n">
-        <v>41.7972164468124</v>
+        <v>53.44993733213093</v>
       </c>
       <c r="P20" t="n">
-        <v>70.52245304170174</v>
+        <v>80.46778072209531</v>
       </c>
       <c r="Q20" t="n">
-        <v>101.6187652513339</v>
+        <v>109.0872921559756</v>
       </c>
       <c r="R20" t="n">
         <v>65.71641987298243</v>
@@ -9457,13 +9457,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J21" t="n">
-        <v>70.34330591194971</v>
+        <v>73.83937108913169</v>
       </c>
       <c r="K21" t="n">
-        <v>41.28364652152882</v>
+        <v>47.25897875440141</v>
       </c>
       <c r="L21" t="n">
-        <v>8.720511855345904</v>
+        <v>16.75508344424118</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -9472,13 +9472,13 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3258104821803158</v>
+        <v>9.130000058643361</v>
       </c>
       <c r="P21" t="n">
-        <v>19.78984137659441</v>
+        <v>26.85597970277001</v>
       </c>
       <c r="Q21" t="n">
-        <v>63.65241559545548</v>
+        <v>68.37594193669796</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9539,22 +9539,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K22" t="n">
-        <v>70.76997948201083</v>
+        <v>74.37427626277801</v>
       </c>
       <c r="L22" t="n">
-        <v>60.35333201894322</v>
+        <v>64.96559098237566</v>
       </c>
       <c r="M22" t="n">
-        <v>60.34293148858869</v>
+        <v>65.20591187910269</v>
       </c>
       <c r="N22" t="n">
-        <v>50.9712165963807</v>
+        <v>55.71856618250388</v>
       </c>
       <c r="O22" t="n">
-        <v>67.59844009118704</v>
+        <v>71.9833858147683</v>
       </c>
       <c r="P22" t="n">
-        <v>77.09665978685257</v>
+        <v>80.84873837615827</v>
       </c>
       <c r="Q22" t="n">
         <v>65.34295837775146</v>
@@ -9615,28 +9615,28 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>86.19202512970136</v>
+        <v>92.06191329280013</v>
       </c>
       <c r="K23" t="n">
-        <v>77.92847416055847</v>
+        <v>86.72591490550931</v>
       </c>
       <c r="L23" t="n">
-        <v>59.40265617601742</v>
+        <v>70.31665934305323</v>
       </c>
       <c r="M23" t="n">
-        <v>34.10756991068988</v>
+        <v>46.25150133729366</v>
       </c>
       <c r="N23" t="n">
-        <v>29.9990535463397</v>
+        <v>42.33948647951536</v>
       </c>
       <c r="O23" t="n">
-        <v>41.7972164468124</v>
+        <v>53.44993733213093</v>
       </c>
       <c r="P23" t="n">
-        <v>70.52245304170174</v>
+        <v>80.46778072209531</v>
       </c>
       <c r="Q23" t="n">
-        <v>101.6187652513339</v>
+        <v>109.0872921559756</v>
       </c>
       <c r="R23" t="n">
         <v>65.71641987298243</v>
@@ -9694,13 +9694,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J24" t="n">
-        <v>70.34330591194971</v>
+        <v>73.83937108913169</v>
       </c>
       <c r="K24" t="n">
-        <v>41.28364652152882</v>
+        <v>47.25897875440141</v>
       </c>
       <c r="L24" t="n">
-        <v>8.720511855345904</v>
+        <v>16.75508344424118</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -9709,13 +9709,13 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0.325810482180259</v>
+        <v>9.130000058643361</v>
       </c>
       <c r="P24" t="n">
-        <v>19.78984137659441</v>
+        <v>26.85597970277001</v>
       </c>
       <c r="Q24" t="n">
-        <v>63.65241559545548</v>
+        <v>68.37594193669796</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9776,22 +9776,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K25" t="n">
-        <v>70.76997948201083</v>
+        <v>74.37427626277801</v>
       </c>
       <c r="L25" t="n">
-        <v>60.35333201894322</v>
+        <v>64.96559098237566</v>
       </c>
       <c r="M25" t="n">
-        <v>60.34293148858869</v>
+        <v>65.20591187910269</v>
       </c>
       <c r="N25" t="n">
-        <v>50.9712165963807</v>
+        <v>55.71856618250388</v>
       </c>
       <c r="O25" t="n">
-        <v>67.59844009118704</v>
+        <v>71.9833858147683</v>
       </c>
       <c r="P25" t="n">
-        <v>77.09665978685257</v>
+        <v>80.84873837615827</v>
       </c>
       <c r="Q25" t="n">
         <v>65.34295837775146</v>
@@ -9852,28 +9852,28 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>86.19202512970136</v>
+        <v>92.06191329280013</v>
       </c>
       <c r="K26" t="n">
-        <v>77.92847416055847</v>
+        <v>86.72591490550931</v>
       </c>
       <c r="L26" t="n">
-        <v>59.40265617601742</v>
+        <v>70.31665934305323</v>
       </c>
       <c r="M26" t="n">
-        <v>34.10756991068988</v>
+        <v>46.25150133729366</v>
       </c>
       <c r="N26" t="n">
-        <v>29.9990535463397</v>
+        <v>42.33948647951536</v>
       </c>
       <c r="O26" t="n">
-        <v>41.7972164468124</v>
+        <v>53.44993733213093</v>
       </c>
       <c r="P26" t="n">
-        <v>70.52245304170174</v>
+        <v>80.46778072209531</v>
       </c>
       <c r="Q26" t="n">
-        <v>101.6187652513339</v>
+        <v>109.0872921559756</v>
       </c>
       <c r="R26" t="n">
         <v>65.71641987298243</v>
@@ -9931,13 +9931,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J27" t="n">
-        <v>70.34330591194971</v>
+        <v>73.83937108913169</v>
       </c>
       <c r="K27" t="n">
-        <v>41.28364652152882</v>
+        <v>47.25897875440141</v>
       </c>
       <c r="L27" t="n">
-        <v>8.720511855345904</v>
+        <v>16.75508344424118</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -9946,13 +9946,13 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>0.325810482180259</v>
+        <v>9.130000058643361</v>
       </c>
       <c r="P27" t="n">
-        <v>19.78984137659441</v>
+        <v>26.85597970277001</v>
       </c>
       <c r="Q27" t="n">
-        <v>63.65241559545548</v>
+        <v>68.37594193669796</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10013,22 +10013,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K28" t="n">
-        <v>70.76997948201083</v>
+        <v>74.37427626277801</v>
       </c>
       <c r="L28" t="n">
-        <v>60.35333201894322</v>
+        <v>64.96559098237566</v>
       </c>
       <c r="M28" t="n">
-        <v>60.34293148858869</v>
+        <v>65.20591187910269</v>
       </c>
       <c r="N28" t="n">
-        <v>50.9712165963807</v>
+        <v>55.71856618250388</v>
       </c>
       <c r="O28" t="n">
-        <v>67.59844009118704</v>
+        <v>71.9833858147683</v>
       </c>
       <c r="P28" t="n">
-        <v>77.09665978685257</v>
+        <v>80.84873837615827</v>
       </c>
       <c r="Q28" t="n">
         <v>65.34295837775146</v>
@@ -10089,28 +10089,28 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>86.19202512970136</v>
+        <v>92.06191329280013</v>
       </c>
       <c r="K29" t="n">
-        <v>77.92847416055847</v>
+        <v>86.72591490550931</v>
       </c>
       <c r="L29" t="n">
-        <v>59.40265617601742</v>
+        <v>70.31665934305323</v>
       </c>
       <c r="M29" t="n">
-        <v>34.10756991068988</v>
+        <v>46.25150133729366</v>
       </c>
       <c r="N29" t="n">
-        <v>29.9990535463397</v>
+        <v>42.33948647951536</v>
       </c>
       <c r="O29" t="n">
-        <v>41.7972164468124</v>
+        <v>53.44993733213093</v>
       </c>
       <c r="P29" t="n">
-        <v>70.52245304170174</v>
+        <v>80.46778072209531</v>
       </c>
       <c r="Q29" t="n">
-        <v>101.6187652513339</v>
+        <v>109.0872921559756</v>
       </c>
       <c r="R29" t="n">
         <v>65.71641987298243</v>
@@ -10168,13 +10168,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J30" t="n">
-        <v>70.34330591194971</v>
+        <v>73.83937108913169</v>
       </c>
       <c r="K30" t="n">
-        <v>41.28364652152882</v>
+        <v>47.25897875440141</v>
       </c>
       <c r="L30" t="n">
-        <v>8.720511855345904</v>
+        <v>16.75508344424118</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -10183,13 +10183,13 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0.3258104821803158</v>
+        <v>9.130000058643361</v>
       </c>
       <c r="P30" t="n">
-        <v>19.78984137659441</v>
+        <v>26.85597970277001</v>
       </c>
       <c r="Q30" t="n">
-        <v>63.65241559545548</v>
+        <v>68.37594193669796</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10250,22 +10250,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K31" t="n">
-        <v>70.76997948201083</v>
+        <v>74.37427626277801</v>
       </c>
       <c r="L31" t="n">
-        <v>60.35333201894322</v>
+        <v>64.96559098237566</v>
       </c>
       <c r="M31" t="n">
-        <v>60.34293148858869</v>
+        <v>65.20591187910269</v>
       </c>
       <c r="N31" t="n">
-        <v>50.9712165963807</v>
+        <v>55.71856618250388</v>
       </c>
       <c r="O31" t="n">
-        <v>67.59844009118704</v>
+        <v>71.9833858147683</v>
       </c>
       <c r="P31" t="n">
-        <v>77.09665978685257</v>
+        <v>80.84873837615827</v>
       </c>
       <c r="Q31" t="n">
         <v>65.34295837775146</v>
@@ -10326,28 +10326,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>86.19202512970136</v>
+        <v>92.06191329280013</v>
       </c>
       <c r="K32" t="n">
-        <v>77.92847416055847</v>
+        <v>86.72591490550931</v>
       </c>
       <c r="L32" t="n">
-        <v>59.40265617601742</v>
+        <v>70.31665934305323</v>
       </c>
       <c r="M32" t="n">
-        <v>34.10756991068988</v>
+        <v>46.25150133729366</v>
       </c>
       <c r="N32" t="n">
-        <v>29.9990535463397</v>
+        <v>42.33948647951536</v>
       </c>
       <c r="O32" t="n">
-        <v>41.7972164468124</v>
+        <v>53.44993733213093</v>
       </c>
       <c r="P32" t="n">
-        <v>70.52245304170174</v>
+        <v>80.46778072209531</v>
       </c>
       <c r="Q32" t="n">
-        <v>101.6187652513339</v>
+        <v>109.0872921559756</v>
       </c>
       <c r="R32" t="n">
         <v>65.71641987298243</v>
@@ -10405,13 +10405,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J33" t="n">
-        <v>70.34330591194971</v>
+        <v>73.83937108913169</v>
       </c>
       <c r="K33" t="n">
-        <v>41.28364652152882</v>
+        <v>47.25897875440141</v>
       </c>
       <c r="L33" t="n">
-        <v>8.720511855345904</v>
+        <v>16.75508344424118</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -10420,13 +10420,13 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>0.3258104821803158</v>
+        <v>9.130000058643361</v>
       </c>
       <c r="P33" t="n">
-        <v>19.78984137659441</v>
+        <v>26.85597970277001</v>
       </c>
       <c r="Q33" t="n">
-        <v>63.65241559545548</v>
+        <v>68.37594193669796</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10487,22 +10487,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K34" t="n">
-        <v>70.76997948201083</v>
+        <v>74.37427626277801</v>
       </c>
       <c r="L34" t="n">
-        <v>60.35333201894322</v>
+        <v>64.96559098237566</v>
       </c>
       <c r="M34" t="n">
-        <v>60.34293148858869</v>
+        <v>65.20591187910269</v>
       </c>
       <c r="N34" t="n">
-        <v>50.9712165963807</v>
+        <v>55.71856618250388</v>
       </c>
       <c r="O34" t="n">
-        <v>67.59844009118704</v>
+        <v>71.9833858147683</v>
       </c>
       <c r="P34" t="n">
-        <v>77.09665978685257</v>
+        <v>80.84873837615827</v>
       </c>
       <c r="Q34" t="n">
         <v>65.34295837775146</v>
@@ -10563,28 +10563,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>86.19202512970136</v>
+        <v>92.06191329280013</v>
       </c>
       <c r="K35" t="n">
-        <v>77.92847416055847</v>
+        <v>86.72591490550931</v>
       </c>
       <c r="L35" t="n">
-        <v>59.40265617601742</v>
+        <v>70.31665934305323</v>
       </c>
       <c r="M35" t="n">
-        <v>34.10756991068988</v>
+        <v>46.25150133729366</v>
       </c>
       <c r="N35" t="n">
-        <v>29.9990535463397</v>
+        <v>42.33948647951536</v>
       </c>
       <c r="O35" t="n">
-        <v>41.7972164468124</v>
+        <v>53.44993733213093</v>
       </c>
       <c r="P35" t="n">
-        <v>70.52245304170174</v>
+        <v>80.46778072209531</v>
       </c>
       <c r="Q35" t="n">
-        <v>101.6187652513339</v>
+        <v>109.0872921559756</v>
       </c>
       <c r="R35" t="n">
         <v>65.71641987298243</v>
@@ -10642,13 +10642,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J36" t="n">
-        <v>70.34330591194971</v>
+        <v>73.83937108913169</v>
       </c>
       <c r="K36" t="n">
-        <v>41.28364652152882</v>
+        <v>47.25897875440141</v>
       </c>
       <c r="L36" t="n">
-        <v>8.720511855345904</v>
+        <v>16.75508344424118</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -10657,13 +10657,13 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>0.3258104821803158</v>
+        <v>9.130000058643361</v>
       </c>
       <c r="P36" t="n">
-        <v>19.78984137659441</v>
+        <v>26.85597970277001</v>
       </c>
       <c r="Q36" t="n">
-        <v>63.65241559545548</v>
+        <v>68.37594193669796</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10724,22 +10724,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K37" t="n">
-        <v>70.76997948201083</v>
+        <v>74.37427626277801</v>
       </c>
       <c r="L37" t="n">
-        <v>60.35333201894322</v>
+        <v>64.96559098237566</v>
       </c>
       <c r="M37" t="n">
-        <v>60.34293148858869</v>
+        <v>65.20591187910269</v>
       </c>
       <c r="N37" t="n">
-        <v>50.9712165963807</v>
+        <v>55.71856618250388</v>
       </c>
       <c r="O37" t="n">
-        <v>67.59844009118704</v>
+        <v>71.9833858147683</v>
       </c>
       <c r="P37" t="n">
-        <v>77.09665978685257</v>
+        <v>80.84873837615827</v>
       </c>
       <c r="Q37" t="n">
         <v>65.34295837775146</v>
@@ -10800,28 +10800,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>86.19202512970136</v>
+        <v>92.06191329280013</v>
       </c>
       <c r="K38" t="n">
-        <v>77.92847416055847</v>
+        <v>86.72591490550931</v>
       </c>
       <c r="L38" t="n">
-        <v>59.40265617601742</v>
+        <v>70.31665934305323</v>
       </c>
       <c r="M38" t="n">
-        <v>34.10756991068988</v>
+        <v>46.25150133729366</v>
       </c>
       <c r="N38" t="n">
-        <v>29.9990535463397</v>
+        <v>42.33948647951536</v>
       </c>
       <c r="O38" t="n">
-        <v>41.7972164468124</v>
+        <v>53.44993733213093</v>
       </c>
       <c r="P38" t="n">
-        <v>70.52245304170174</v>
+        <v>80.46778072209531</v>
       </c>
       <c r="Q38" t="n">
-        <v>101.6187652513339</v>
+        <v>109.0872921559756</v>
       </c>
       <c r="R38" t="n">
         <v>65.71641987298243</v>
@@ -10879,13 +10879,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J39" t="n">
-        <v>70.34330591194971</v>
+        <v>73.83937108913169</v>
       </c>
       <c r="K39" t="n">
-        <v>41.28364652152882</v>
+        <v>47.25897875440141</v>
       </c>
       <c r="L39" t="n">
-        <v>8.720511855345904</v>
+        <v>16.75508344424118</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -10894,13 +10894,13 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>0.3258104821803158</v>
+        <v>9.130000058643361</v>
       </c>
       <c r="P39" t="n">
-        <v>19.78984137659441</v>
+        <v>26.85597970277001</v>
       </c>
       <c r="Q39" t="n">
-        <v>63.65241559545548</v>
+        <v>68.37594193669796</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -10961,22 +10961,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K40" t="n">
-        <v>70.76997948201083</v>
+        <v>74.37427626277801</v>
       </c>
       <c r="L40" t="n">
-        <v>60.35333201894322</v>
+        <v>64.96559098237566</v>
       </c>
       <c r="M40" t="n">
-        <v>60.34293148858869</v>
+        <v>65.20591187910269</v>
       </c>
       <c r="N40" t="n">
-        <v>50.9712165963807</v>
+        <v>55.71856618250388</v>
       </c>
       <c r="O40" t="n">
-        <v>67.59844009118704</v>
+        <v>71.9833858147683</v>
       </c>
       <c r="P40" t="n">
-        <v>77.09665978685257</v>
+        <v>80.84873837615827</v>
       </c>
       <c r="Q40" t="n">
         <v>65.34295837775146</v>
@@ -11037,28 +11037,28 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>86.19202512970136</v>
+        <v>92.06191329280013</v>
       </c>
       <c r="K41" t="n">
-        <v>77.92847416055847</v>
+        <v>86.72591490550931</v>
       </c>
       <c r="L41" t="n">
-        <v>59.40265617601742</v>
+        <v>70.31665934305323</v>
       </c>
       <c r="M41" t="n">
-        <v>34.10756991068988</v>
+        <v>46.25150133729366</v>
       </c>
       <c r="N41" t="n">
-        <v>29.9990535463397</v>
+        <v>42.33948647951536</v>
       </c>
       <c r="O41" t="n">
-        <v>41.7972164468124</v>
+        <v>53.44993733213093</v>
       </c>
       <c r="P41" t="n">
-        <v>70.52245304170174</v>
+        <v>80.46778072209531</v>
       </c>
       <c r="Q41" t="n">
-        <v>101.6187652513339</v>
+        <v>109.0872921559756</v>
       </c>
       <c r="R41" t="n">
         <v>65.71641987298243</v>
@@ -11116,13 +11116,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J42" t="n">
-        <v>70.34330591194971</v>
+        <v>73.83937108913169</v>
       </c>
       <c r="K42" t="n">
-        <v>41.28364652152882</v>
+        <v>47.25897875440141</v>
       </c>
       <c r="L42" t="n">
-        <v>8.720511855345904</v>
+        <v>16.75508344424118</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -11131,13 +11131,13 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>0.3258104821803158</v>
+        <v>9.130000058643361</v>
       </c>
       <c r="P42" t="n">
-        <v>19.78984137659441</v>
+        <v>26.85597970277001</v>
       </c>
       <c r="Q42" t="n">
-        <v>63.65241559545548</v>
+        <v>68.37594193669796</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11198,22 +11198,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K43" t="n">
-        <v>70.76997948201083</v>
+        <v>74.37427626277801</v>
       </c>
       <c r="L43" t="n">
-        <v>60.35333201894322</v>
+        <v>64.96559098237566</v>
       </c>
       <c r="M43" t="n">
-        <v>60.34293148858869</v>
+        <v>65.20591187910269</v>
       </c>
       <c r="N43" t="n">
-        <v>50.9712165963807</v>
+        <v>55.71856618250388</v>
       </c>
       <c r="O43" t="n">
-        <v>67.59844009118704</v>
+        <v>71.9833858147683</v>
       </c>
       <c r="P43" t="n">
-        <v>77.09665978685257</v>
+        <v>80.84873837615827</v>
       </c>
       <c r="Q43" t="n">
         <v>65.34295837775146</v>
@@ -11274,28 +11274,28 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>86.19202512970136</v>
+        <v>92.06191329280013</v>
       </c>
       <c r="K44" t="n">
-        <v>77.92847416055847</v>
+        <v>86.72591490550931</v>
       </c>
       <c r="L44" t="n">
-        <v>59.40265617601742</v>
+        <v>70.31665934305323</v>
       </c>
       <c r="M44" t="n">
-        <v>34.10756991068988</v>
+        <v>46.25150133729366</v>
       </c>
       <c r="N44" t="n">
-        <v>29.9990535463397</v>
+        <v>42.33948647951536</v>
       </c>
       <c r="O44" t="n">
-        <v>41.7972164468124</v>
+        <v>53.44993733213093</v>
       </c>
       <c r="P44" t="n">
-        <v>70.52245304170174</v>
+        <v>80.46778072209531</v>
       </c>
       <c r="Q44" t="n">
-        <v>101.6187652513339</v>
+        <v>109.0872921559756</v>
       </c>
       <c r="R44" t="n">
         <v>65.71641987298243</v>
@@ -11353,13 +11353,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J45" t="n">
-        <v>70.34330591194971</v>
+        <v>73.83937108913169</v>
       </c>
       <c r="K45" t="n">
-        <v>41.28364652152882</v>
+        <v>47.25897875440141</v>
       </c>
       <c r="L45" t="n">
-        <v>8.720511855345904</v>
+        <v>16.75508344424118</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -11368,13 +11368,13 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>0.3258104821803158</v>
+        <v>9.130000058643361</v>
       </c>
       <c r="P45" t="n">
-        <v>19.78984137659441</v>
+        <v>26.85597970277001</v>
       </c>
       <c r="Q45" t="n">
-        <v>63.65241559545548</v>
+        <v>68.37594193669796</v>
       </c>
       <c r="R45" t="n">
         <v>45.52166981132082</v>
@@ -11435,22 +11435,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K46" t="n">
-        <v>70.76997948201083</v>
+        <v>74.37427626277801</v>
       </c>
       <c r="L46" t="n">
-        <v>60.35333201894322</v>
+        <v>64.96559098237566</v>
       </c>
       <c r="M46" t="n">
-        <v>60.34293148858869</v>
+        <v>65.20591187910269</v>
       </c>
       <c r="N46" t="n">
-        <v>50.9712165963807</v>
+        <v>55.71856618250388</v>
       </c>
       <c r="O46" t="n">
-        <v>67.59844009118704</v>
+        <v>71.9833858147683</v>
       </c>
       <c r="P46" t="n">
-        <v>77.09665978685257</v>
+        <v>80.84873837615827</v>
       </c>
       <c r="Q46" t="n">
         <v>65.34295837775146</v>
@@ -23230,13 +23230,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G11" t="n">
-        <v>414.1851495754366</v>
+        <v>414.2543098065221</v>
       </c>
       <c r="H11" t="n">
-        <v>328.02930462833</v>
+        <v>328.737591844935</v>
       </c>
       <c r="I11" t="n">
-        <v>167.3900805251798</v>
+        <v>170.0563803341062</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -23263,16 +23263,16 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>79.66643452406426</v>
+        <v>84.0108208899931</v>
       </c>
       <c r="S11" t="n">
-        <v>183.5530344103659</v>
+        <v>185.1290231762283</v>
       </c>
       <c r="T11" t="n">
-        <v>218.2036083581012</v>
+        <v>218.5063572696783</v>
       </c>
       <c r="U11" t="n">
-        <v>251.2562458726606</v>
+        <v>251.2617786911475</v>
       </c>
       <c r="V11" t="n">
         <v>327.7522584701349</v>
@@ -23309,13 +23309,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G12" t="n">
-        <v>136.7455548990597</v>
+        <v>136.7825588849655</v>
       </c>
       <c r="H12" t="n">
-        <v>106.4603876327229</v>
+        <v>106.817768233445</v>
       </c>
       <c r="I12" t="n">
-        <v>68.80889700235848</v>
+        <v>70.08293774516886</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -23342,16 +23342,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>63.03172094509596</v>
+        <v>65.32921403493339</v>
       </c>
       <c r="S12" t="n">
-        <v>160.576284311385</v>
+        <v>161.2636171197674</v>
       </c>
       <c r="T12" t="n">
-        <v>197.7545211476518</v>
+        <v>197.9036731785617</v>
       </c>
       <c r="U12" t="n">
-        <v>225.9020424583333</v>
+        <v>225.9044769310903</v>
       </c>
       <c r="V12" t="n">
         <v>232.8005871494253</v>
@@ -23388,16 +23388,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G13" t="n">
-        <v>167.4896678830489</v>
+        <v>167.5206907817879</v>
       </c>
       <c r="H13" t="n">
-        <v>157.7700577533412</v>
+        <v>158.0458795257661</v>
       </c>
       <c r="I13" t="n">
-        <v>140.3746716485697</v>
+        <v>141.3076148215571</v>
       </c>
       <c r="J13" t="n">
-        <v>57.91645880519738</v>
+        <v>60.10977774604452</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -23418,19 +23418,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>44.1840432516944</v>
+        <v>46.7817879815572</v>
       </c>
       <c r="R13" t="n">
-        <v>154.7526044919236</v>
+        <v>156.1475068297698</v>
       </c>
       <c r="S13" t="n">
-        <v>215.2801062336936</v>
+        <v>215.8207507508087</v>
       </c>
       <c r="T13" t="n">
-        <v>225.8036222151667</v>
+        <v>225.9361746006879</v>
       </c>
       <c r="U13" t="n">
-        <v>286.2916850941958</v>
+        <v>286.2933772523089</v>
       </c>
       <c r="V13" t="n">
         <v>252.137643323828</v>
@@ -23467,13 +23467,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G14" t="n">
-        <v>414.1851495754366</v>
+        <v>414.2543098065221</v>
       </c>
       <c r="H14" t="n">
-        <v>328.02930462833</v>
+        <v>328.737591844935</v>
       </c>
       <c r="I14" t="n">
-        <v>167.3900805251798</v>
+        <v>170.0563803341062</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -23500,16 +23500,16 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>79.66643452406426</v>
+        <v>84.0108208899931</v>
       </c>
       <c r="S14" t="n">
-        <v>183.5530344103659</v>
+        <v>185.1290231762283</v>
       </c>
       <c r="T14" t="n">
-        <v>218.2036083581012</v>
+        <v>218.5063572696783</v>
       </c>
       <c r="U14" t="n">
-        <v>251.2562458726606</v>
+        <v>251.2617786911475</v>
       </c>
       <c r="V14" t="n">
         <v>327.7522584701349</v>
@@ -23546,13 +23546,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
-        <v>136.7455548990597</v>
+        <v>136.7825588849655</v>
       </c>
       <c r="H15" t="n">
-        <v>106.4603876327229</v>
+        <v>106.817768233445</v>
       </c>
       <c r="I15" t="n">
-        <v>68.80889700235848</v>
+        <v>70.08293774516886</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -23579,16 +23579,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>63.03172094509596</v>
+        <v>65.32921403493339</v>
       </c>
       <c r="S15" t="n">
-        <v>160.576284311385</v>
+        <v>161.2636171197674</v>
       </c>
       <c r="T15" t="n">
-        <v>197.7545211476518</v>
+        <v>197.9036731785617</v>
       </c>
       <c r="U15" t="n">
-        <v>225.9020424583333</v>
+        <v>225.9044769310903</v>
       </c>
       <c r="V15" t="n">
         <v>232.8005871494253</v>
@@ -23625,16 +23625,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G16" t="n">
-        <v>167.4896678830489</v>
+        <v>167.5206907817879</v>
       </c>
       <c r="H16" t="n">
-        <v>157.7700577533412</v>
+        <v>158.0458795257661</v>
       </c>
       <c r="I16" t="n">
-        <v>140.3746716485697</v>
+        <v>141.3076148215571</v>
       </c>
       <c r="J16" t="n">
-        <v>57.91645880519738</v>
+        <v>60.10977774604452</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -23655,19 +23655,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>44.1840432516944</v>
+        <v>46.7817879815572</v>
       </c>
       <c r="R16" t="n">
-        <v>154.7526044919236</v>
+        <v>156.1475068297698</v>
       </c>
       <c r="S16" t="n">
-        <v>215.2801062336936</v>
+        <v>215.8207507508087</v>
       </c>
       <c r="T16" t="n">
-        <v>225.8036222151667</v>
+        <v>225.9361746006879</v>
       </c>
       <c r="U16" t="n">
-        <v>286.2916850941958</v>
+        <v>286.2933772523089</v>
       </c>
       <c r="V16" t="n">
         <v>252.137643323828</v>
@@ -23704,13 +23704,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G17" t="n">
-        <v>414.1851495754366</v>
+        <v>414.2543098065221</v>
       </c>
       <c r="H17" t="n">
-        <v>328.02930462833</v>
+        <v>328.737591844935</v>
       </c>
       <c r="I17" t="n">
-        <v>167.3900805251798</v>
+        <v>170.0563803341062</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -23737,16 +23737,16 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>79.66643452406426</v>
+        <v>84.01082088999308</v>
       </c>
       <c r="S17" t="n">
-        <v>183.5530344103659</v>
+        <v>185.1290231762283</v>
       </c>
       <c r="T17" t="n">
-        <v>218.2036083581012</v>
+        <v>218.5063572696783</v>
       </c>
       <c r="U17" t="n">
-        <v>251.2562458726606</v>
+        <v>251.2617786911475</v>
       </c>
       <c r="V17" t="n">
         <v>327.7522584701349</v>
@@ -23783,13 +23783,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G18" t="n">
-        <v>136.7455548990597</v>
+        <v>136.7825588849655</v>
       </c>
       <c r="H18" t="n">
-        <v>106.4603876327229</v>
+        <v>106.817768233445</v>
       </c>
       <c r="I18" t="n">
-        <v>68.80889700235848</v>
+        <v>70.08293774516886</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -23816,16 +23816,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>63.03172094509596</v>
+        <v>65.32921403493339</v>
       </c>
       <c r="S18" t="n">
-        <v>160.576284311385</v>
+        <v>161.2636171197674</v>
       </c>
       <c r="T18" t="n">
-        <v>197.7545211476518</v>
+        <v>197.9036731785617</v>
       </c>
       <c r="U18" t="n">
-        <v>225.9020424583333</v>
+        <v>225.9044769310903</v>
       </c>
       <c r="V18" t="n">
         <v>232.8005871494253</v>
@@ -23862,16 +23862,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G19" t="n">
-        <v>167.4896678830489</v>
+        <v>167.5206907817879</v>
       </c>
       <c r="H19" t="n">
-        <v>157.7700577533412</v>
+        <v>158.0458795257661</v>
       </c>
       <c r="I19" t="n">
-        <v>140.3746716485697</v>
+        <v>141.3076148215571</v>
       </c>
       <c r="J19" t="n">
-        <v>57.91645880519738</v>
+        <v>60.10977774604451</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -23892,19 +23892,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>44.1840432516944</v>
+        <v>46.78178798155719</v>
       </c>
       <c r="R19" t="n">
-        <v>154.7526044919236</v>
+        <v>156.1475068297698</v>
       </c>
       <c r="S19" t="n">
-        <v>215.2801062336936</v>
+        <v>215.8207507508087</v>
       </c>
       <c r="T19" t="n">
-        <v>225.8036222151667</v>
+        <v>225.9361746006879</v>
       </c>
       <c r="U19" t="n">
-        <v>286.2916850941958</v>
+        <v>286.2933772523089</v>
       </c>
       <c r="V19" t="n">
         <v>252.137643323828</v>
@@ -23941,13 +23941,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>414.1851495754366</v>
+        <v>414.2543098065221</v>
       </c>
       <c r="H20" t="n">
-        <v>328.02930462833</v>
+        <v>328.737591844935</v>
       </c>
       <c r="I20" t="n">
-        <v>167.3900805251798</v>
+        <v>170.0563803341062</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -23974,16 +23974,16 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>79.66643452406426</v>
+        <v>84.0108208899931</v>
       </c>
       <c r="S20" t="n">
-        <v>183.5530344103659</v>
+        <v>185.1290231762283</v>
       </c>
       <c r="T20" t="n">
-        <v>218.2036083581012</v>
+        <v>218.5063572696783</v>
       </c>
       <c r="U20" t="n">
-        <v>251.2562458726606</v>
+        <v>251.2617786911475</v>
       </c>
       <c r="V20" t="n">
         <v>327.7522584701349</v>
@@ -24020,13 +24020,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>136.7455548990597</v>
+        <v>136.7825588849655</v>
       </c>
       <c r="H21" t="n">
-        <v>106.4603876327229</v>
+        <v>106.817768233445</v>
       </c>
       <c r="I21" t="n">
-        <v>68.80889700235848</v>
+        <v>70.08293774516886</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -24053,16 +24053,16 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>63.03172094509596</v>
+        <v>65.32921403493339</v>
       </c>
       <c r="S21" t="n">
-        <v>160.576284311385</v>
+        <v>161.2636171197674</v>
       </c>
       <c r="T21" t="n">
-        <v>197.7545211476518</v>
+        <v>197.9036731785617</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9020424583333</v>
+        <v>225.9044769310903</v>
       </c>
       <c r="V21" t="n">
         <v>232.8005871494253</v>
@@ -24099,16 +24099,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G22" t="n">
-        <v>167.4896678830489</v>
+        <v>167.5206907817879</v>
       </c>
       <c r="H22" t="n">
-        <v>157.7700577533412</v>
+        <v>158.0458795257661</v>
       </c>
       <c r="I22" t="n">
-        <v>140.3746716485697</v>
+        <v>141.3076148215571</v>
       </c>
       <c r="J22" t="n">
-        <v>57.91645880519738</v>
+        <v>60.10977774604452</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -24129,19 +24129,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>44.1840432516944</v>
+        <v>46.7817879815572</v>
       </c>
       <c r="R22" t="n">
-        <v>154.7526044919236</v>
+        <v>156.1475068297698</v>
       </c>
       <c r="S22" t="n">
-        <v>215.2801062336936</v>
+        <v>215.8207507508087</v>
       </c>
       <c r="T22" t="n">
-        <v>225.8036222151667</v>
+        <v>225.9361746006879</v>
       </c>
       <c r="U22" t="n">
-        <v>286.2916850941958</v>
+        <v>286.2933772523089</v>
       </c>
       <c r="V22" t="n">
         <v>252.137643323828</v>
@@ -24178,13 +24178,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
-        <v>414.1851495754366</v>
+        <v>414.2543098065221</v>
       </c>
       <c r="H23" t="n">
-        <v>328.02930462833</v>
+        <v>328.737591844935</v>
       </c>
       <c r="I23" t="n">
-        <v>167.3900805251798</v>
+        <v>170.0563803341062</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -24211,16 +24211,16 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>79.66643452406426</v>
+        <v>84.0108208899931</v>
       </c>
       <c r="S23" t="n">
-        <v>183.5530344103659</v>
+        <v>185.1290231762283</v>
       </c>
       <c r="T23" t="n">
-        <v>218.2036083581012</v>
+        <v>218.5063572696783</v>
       </c>
       <c r="U23" t="n">
-        <v>251.2562458726606</v>
+        <v>251.2617786911475</v>
       </c>
       <c r="V23" t="n">
         <v>327.7522584701349</v>
@@ -24257,13 +24257,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>136.7455548990597</v>
+        <v>136.7825588849655</v>
       </c>
       <c r="H24" t="n">
-        <v>106.4603876327229</v>
+        <v>106.817768233445</v>
       </c>
       <c r="I24" t="n">
-        <v>68.80889700235848</v>
+        <v>70.08293774516886</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -24290,16 +24290,16 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>63.03172094509596</v>
+        <v>65.32921403493339</v>
       </c>
       <c r="S24" t="n">
-        <v>160.576284311385</v>
+        <v>161.2636171197674</v>
       </c>
       <c r="T24" t="n">
-        <v>197.7545211476518</v>
+        <v>197.9036731785617</v>
       </c>
       <c r="U24" t="n">
-        <v>225.9020424583333</v>
+        <v>225.9044769310903</v>
       </c>
       <c r="V24" t="n">
         <v>232.8005871494253</v>
@@ -24336,16 +24336,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G25" t="n">
-        <v>167.4896678830489</v>
+        <v>167.5206907817879</v>
       </c>
       <c r="H25" t="n">
-        <v>157.7700577533412</v>
+        <v>158.0458795257661</v>
       </c>
       <c r="I25" t="n">
-        <v>140.3746716485697</v>
+        <v>141.3076148215571</v>
       </c>
       <c r="J25" t="n">
-        <v>57.91645880519738</v>
+        <v>60.10977774604452</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -24366,19 +24366,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>44.1840432516944</v>
+        <v>46.7817879815572</v>
       </c>
       <c r="R25" t="n">
-        <v>154.7526044919236</v>
+        <v>156.1475068297698</v>
       </c>
       <c r="S25" t="n">
-        <v>215.2801062336936</v>
+        <v>215.8207507508087</v>
       </c>
       <c r="T25" t="n">
-        <v>225.8036222151667</v>
+        <v>225.9361746006879</v>
       </c>
       <c r="U25" t="n">
-        <v>286.2916850941958</v>
+        <v>286.2933772523089</v>
       </c>
       <c r="V25" t="n">
         <v>252.137643323828</v>
@@ -24415,13 +24415,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G26" t="n">
-        <v>414.1851495754366</v>
+        <v>414.2543098065221</v>
       </c>
       <c r="H26" t="n">
-        <v>328.02930462833</v>
+        <v>328.737591844935</v>
       </c>
       <c r="I26" t="n">
-        <v>167.3900805251798</v>
+        <v>170.0563803341062</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -24448,16 +24448,16 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>79.66643452406426</v>
+        <v>84.0108208899931</v>
       </c>
       <c r="S26" t="n">
-        <v>183.5530344103659</v>
+        <v>185.1290231762283</v>
       </c>
       <c r="T26" t="n">
-        <v>218.2036083581012</v>
+        <v>218.5063572696783</v>
       </c>
       <c r="U26" t="n">
-        <v>251.2562458726606</v>
+        <v>251.2617786911475</v>
       </c>
       <c r="V26" t="n">
         <v>327.7522584701349</v>
@@ -24494,13 +24494,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>136.7455548990597</v>
+        <v>136.7825588849655</v>
       </c>
       <c r="H27" t="n">
-        <v>106.4603876327229</v>
+        <v>106.817768233445</v>
       </c>
       <c r="I27" t="n">
-        <v>68.80889700235848</v>
+        <v>70.08293774516886</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -24527,16 +24527,16 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>63.03172094509596</v>
+        <v>65.32921403493339</v>
       </c>
       <c r="S27" t="n">
-        <v>160.576284311385</v>
+        <v>161.2636171197674</v>
       </c>
       <c r="T27" t="n">
-        <v>197.7545211476518</v>
+        <v>197.9036731785617</v>
       </c>
       <c r="U27" t="n">
-        <v>225.9020424583333</v>
+        <v>225.9044769310903</v>
       </c>
       <c r="V27" t="n">
         <v>232.8005871494253</v>
@@ -24573,16 +24573,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G28" t="n">
-        <v>167.4896678830489</v>
+        <v>167.5206907817879</v>
       </c>
       <c r="H28" t="n">
-        <v>157.7700577533412</v>
+        <v>158.0458795257661</v>
       </c>
       <c r="I28" t="n">
-        <v>140.3746716485697</v>
+        <v>141.3076148215571</v>
       </c>
       <c r="J28" t="n">
-        <v>57.91645880519738</v>
+        <v>60.10977774604452</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -24603,19 +24603,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>44.1840432516944</v>
+        <v>46.7817879815572</v>
       </c>
       <c r="R28" t="n">
-        <v>154.7526044919236</v>
+        <v>156.1475068297698</v>
       </c>
       <c r="S28" t="n">
-        <v>215.2801062336936</v>
+        <v>215.8207507508087</v>
       </c>
       <c r="T28" t="n">
-        <v>225.8036222151667</v>
+        <v>225.9361746006879</v>
       </c>
       <c r="U28" t="n">
-        <v>286.2916850941958</v>
+        <v>286.2933772523089</v>
       </c>
       <c r="V28" t="n">
         <v>252.137643323828</v>
@@ -24652,13 +24652,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
-        <v>414.1851495754366</v>
+        <v>414.2543098065221</v>
       </c>
       <c r="H29" t="n">
-        <v>328.02930462833</v>
+        <v>328.737591844935</v>
       </c>
       <c r="I29" t="n">
-        <v>167.3900805251798</v>
+        <v>170.0563803341062</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -24685,16 +24685,16 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>79.66643452406426</v>
+        <v>84.0108208899931</v>
       </c>
       <c r="S29" t="n">
-        <v>183.5530344103659</v>
+        <v>185.1290231762283</v>
       </c>
       <c r="T29" t="n">
-        <v>218.2036083581012</v>
+        <v>218.5063572696783</v>
       </c>
       <c r="U29" t="n">
-        <v>251.2562458726606</v>
+        <v>251.2617786911475</v>
       </c>
       <c r="V29" t="n">
         <v>327.7522584701349</v>
@@ -24731,13 +24731,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>136.7455548990597</v>
+        <v>136.7825588849655</v>
       </c>
       <c r="H30" t="n">
-        <v>106.4603876327229</v>
+        <v>106.817768233445</v>
       </c>
       <c r="I30" t="n">
-        <v>68.80889700235848</v>
+        <v>70.08293774516886</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -24764,16 +24764,16 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>63.03172094509596</v>
+        <v>65.32921403493339</v>
       </c>
       <c r="S30" t="n">
-        <v>160.576284311385</v>
+        <v>161.2636171197674</v>
       </c>
       <c r="T30" t="n">
-        <v>197.7545211476518</v>
+        <v>197.9036731785617</v>
       </c>
       <c r="U30" t="n">
-        <v>225.9020424583333</v>
+        <v>225.9044769310903</v>
       </c>
       <c r="V30" t="n">
         <v>232.8005871494253</v>
@@ -24810,16 +24810,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G31" t="n">
-        <v>167.4896678830489</v>
+        <v>167.5206907817879</v>
       </c>
       <c r="H31" t="n">
-        <v>157.7700577533412</v>
+        <v>158.0458795257661</v>
       </c>
       <c r="I31" t="n">
-        <v>140.3746716485697</v>
+        <v>141.3076148215571</v>
       </c>
       <c r="J31" t="n">
-        <v>57.91645880519738</v>
+        <v>60.10977774604452</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -24840,19 +24840,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>44.1840432516944</v>
+        <v>46.7817879815572</v>
       </c>
       <c r="R31" t="n">
-        <v>154.7526044919236</v>
+        <v>156.1475068297698</v>
       </c>
       <c r="S31" t="n">
-        <v>215.2801062336936</v>
+        <v>215.8207507508087</v>
       </c>
       <c r="T31" t="n">
-        <v>225.8036222151667</v>
+        <v>225.9361746006879</v>
       </c>
       <c r="U31" t="n">
-        <v>286.2916850941958</v>
+        <v>286.2933772523089</v>
       </c>
       <c r="V31" t="n">
         <v>252.137643323828</v>
@@ -24889,13 +24889,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>414.1851495754366</v>
+        <v>414.2543098065221</v>
       </c>
       <c r="H32" t="n">
-        <v>328.02930462833</v>
+        <v>328.737591844935</v>
       </c>
       <c r="I32" t="n">
-        <v>167.3900805251798</v>
+        <v>170.0563803341062</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -24922,16 +24922,16 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>79.66643452406426</v>
+        <v>84.0108208899931</v>
       </c>
       <c r="S32" t="n">
-        <v>183.5530344103659</v>
+        <v>185.1290231762283</v>
       </c>
       <c r="T32" t="n">
-        <v>218.2036083581012</v>
+        <v>218.5063572696783</v>
       </c>
       <c r="U32" t="n">
-        <v>251.2562458726606</v>
+        <v>251.2617786911475</v>
       </c>
       <c r="V32" t="n">
         <v>327.7522584701349</v>
@@ -24968,13 +24968,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>136.7455548990597</v>
+        <v>136.7825588849655</v>
       </c>
       <c r="H33" t="n">
-        <v>106.4603876327229</v>
+        <v>106.817768233445</v>
       </c>
       <c r="I33" t="n">
-        <v>68.80889700235848</v>
+        <v>70.08293774516886</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -25001,16 +25001,16 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>63.03172094509596</v>
+        <v>65.32921403493339</v>
       </c>
       <c r="S33" t="n">
-        <v>160.576284311385</v>
+        <v>161.2636171197674</v>
       </c>
       <c r="T33" t="n">
-        <v>197.7545211476518</v>
+        <v>197.9036731785617</v>
       </c>
       <c r="U33" t="n">
-        <v>225.9020424583333</v>
+        <v>225.9044769310903</v>
       </c>
       <c r="V33" t="n">
         <v>232.8005871494253</v>
@@ -25047,16 +25047,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G34" t="n">
-        <v>167.4896678830489</v>
+        <v>167.5206907817879</v>
       </c>
       <c r="H34" t="n">
-        <v>157.7700577533412</v>
+        <v>158.0458795257661</v>
       </c>
       <c r="I34" t="n">
-        <v>140.3746716485697</v>
+        <v>141.3076148215571</v>
       </c>
       <c r="J34" t="n">
-        <v>57.91645880519738</v>
+        <v>60.10977774604452</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -25077,19 +25077,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>44.1840432516944</v>
+        <v>46.7817879815572</v>
       </c>
       <c r="R34" t="n">
-        <v>154.7526044919236</v>
+        <v>156.1475068297698</v>
       </c>
       <c r="S34" t="n">
-        <v>215.2801062336936</v>
+        <v>215.8207507508087</v>
       </c>
       <c r="T34" t="n">
-        <v>225.8036222151667</v>
+        <v>225.9361746006879</v>
       </c>
       <c r="U34" t="n">
-        <v>286.2916850941958</v>
+        <v>286.2933772523089</v>
       </c>
       <c r="V34" t="n">
         <v>252.137643323828</v>
@@ -25126,13 +25126,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G35" t="n">
-        <v>414.1851495754366</v>
+        <v>414.2543098065221</v>
       </c>
       <c r="H35" t="n">
-        <v>328.02930462833</v>
+        <v>328.737591844935</v>
       </c>
       <c r="I35" t="n">
-        <v>167.3900805251798</v>
+        <v>170.0563803341062</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -25159,16 +25159,16 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>79.66643452406426</v>
+        <v>84.0108208899931</v>
       </c>
       <c r="S35" t="n">
-        <v>183.5530344103659</v>
+        <v>185.1290231762283</v>
       </c>
       <c r="T35" t="n">
-        <v>218.2036083581012</v>
+        <v>218.5063572696783</v>
       </c>
       <c r="U35" t="n">
-        <v>251.2562458726606</v>
+        <v>251.2617786911475</v>
       </c>
       <c r="V35" t="n">
         <v>327.7522584701349</v>
@@ -25205,13 +25205,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
-        <v>136.7455548990597</v>
+        <v>136.7825588849655</v>
       </c>
       <c r="H36" t="n">
-        <v>106.4603876327229</v>
+        <v>106.817768233445</v>
       </c>
       <c r="I36" t="n">
-        <v>68.80889700235848</v>
+        <v>70.08293774516886</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -25238,16 +25238,16 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>63.03172094509596</v>
+        <v>65.32921403493339</v>
       </c>
       <c r="S36" t="n">
-        <v>160.576284311385</v>
+        <v>161.2636171197674</v>
       </c>
       <c r="T36" t="n">
-        <v>197.7545211476518</v>
+        <v>197.9036731785617</v>
       </c>
       <c r="U36" t="n">
-        <v>225.9020424583333</v>
+        <v>225.9044769310903</v>
       </c>
       <c r="V36" t="n">
         <v>232.8005871494253</v>
@@ -25284,16 +25284,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G37" t="n">
-        <v>167.4896678830489</v>
+        <v>167.5206907817879</v>
       </c>
       <c r="H37" t="n">
-        <v>157.7700577533412</v>
+        <v>158.0458795257661</v>
       </c>
       <c r="I37" t="n">
-        <v>140.3746716485697</v>
+        <v>141.3076148215571</v>
       </c>
       <c r="J37" t="n">
-        <v>57.91645880519738</v>
+        <v>60.10977774604452</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -25314,19 +25314,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>44.1840432516944</v>
+        <v>46.7817879815572</v>
       </c>
       <c r="R37" t="n">
-        <v>154.7526044919236</v>
+        <v>156.1475068297698</v>
       </c>
       <c r="S37" t="n">
-        <v>215.2801062336936</v>
+        <v>215.8207507508087</v>
       </c>
       <c r="T37" t="n">
-        <v>225.8036222151667</v>
+        <v>225.9361746006879</v>
       </c>
       <c r="U37" t="n">
-        <v>286.2916850941958</v>
+        <v>286.2933772523089</v>
       </c>
       <c r="V37" t="n">
         <v>252.137643323828</v>
@@ -25363,13 +25363,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>414.1851495754366</v>
+        <v>414.2543098065221</v>
       </c>
       <c r="H38" t="n">
-        <v>328.02930462833</v>
+        <v>328.737591844935</v>
       </c>
       <c r="I38" t="n">
-        <v>167.3900805251798</v>
+        <v>170.0563803341062</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -25396,16 +25396,16 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>79.66643452406426</v>
+        <v>84.0108208899931</v>
       </c>
       <c r="S38" t="n">
-        <v>183.5530344103659</v>
+        <v>185.1290231762283</v>
       </c>
       <c r="T38" t="n">
-        <v>218.2036083581012</v>
+        <v>218.5063572696783</v>
       </c>
       <c r="U38" t="n">
-        <v>251.2562458726606</v>
+        <v>251.2617786911475</v>
       </c>
       <c r="V38" t="n">
         <v>327.7522584701349</v>
@@ -25442,13 +25442,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>136.7455548990597</v>
+        <v>136.7825588849655</v>
       </c>
       <c r="H39" t="n">
-        <v>106.4603876327229</v>
+        <v>106.817768233445</v>
       </c>
       <c r="I39" t="n">
-        <v>68.80889700235848</v>
+        <v>70.08293774516886</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -25475,16 +25475,16 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>63.03172094509596</v>
+        <v>65.32921403493339</v>
       </c>
       <c r="S39" t="n">
-        <v>160.576284311385</v>
+        <v>161.2636171197674</v>
       </c>
       <c r="T39" t="n">
-        <v>197.7545211476518</v>
+        <v>197.9036731785617</v>
       </c>
       <c r="U39" t="n">
-        <v>225.9020424583333</v>
+        <v>225.9044769310903</v>
       </c>
       <c r="V39" t="n">
         <v>232.8005871494253</v>
@@ -25521,16 +25521,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G40" t="n">
-        <v>167.4896678830489</v>
+        <v>167.5206907817879</v>
       </c>
       <c r="H40" t="n">
-        <v>157.7700577533412</v>
+        <v>158.0458795257661</v>
       </c>
       <c r="I40" t="n">
-        <v>140.3746716485697</v>
+        <v>141.3076148215571</v>
       </c>
       <c r="J40" t="n">
-        <v>57.91645880519738</v>
+        <v>60.10977774604452</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -25551,19 +25551,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>44.1840432516944</v>
+        <v>46.7817879815572</v>
       </c>
       <c r="R40" t="n">
-        <v>154.7526044919236</v>
+        <v>156.1475068297698</v>
       </c>
       <c r="S40" t="n">
-        <v>215.2801062336936</v>
+        <v>215.8207507508087</v>
       </c>
       <c r="T40" t="n">
-        <v>225.8036222151667</v>
+        <v>225.9361746006879</v>
       </c>
       <c r="U40" t="n">
-        <v>286.2916850941958</v>
+        <v>286.2933772523089</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
@@ -25600,13 +25600,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>414.1851495754366</v>
+        <v>414.2543098065221</v>
       </c>
       <c r="H41" t="n">
-        <v>328.02930462833</v>
+        <v>328.737591844935</v>
       </c>
       <c r="I41" t="n">
-        <v>167.3900805251798</v>
+        <v>170.0563803341062</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -25633,16 +25633,16 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>79.66643452406426</v>
+        <v>84.0108208899931</v>
       </c>
       <c r="S41" t="n">
-        <v>183.5530344103659</v>
+        <v>185.1290231762283</v>
       </c>
       <c r="T41" t="n">
-        <v>218.2036083581012</v>
+        <v>218.5063572696783</v>
       </c>
       <c r="U41" t="n">
-        <v>251.2562458726606</v>
+        <v>251.2617786911475</v>
       </c>
       <c r="V41" t="n">
         <v>327.7522584701349</v>
@@ -25679,13 +25679,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
-        <v>136.7455548990597</v>
+        <v>136.7825588849655</v>
       </c>
       <c r="H42" t="n">
-        <v>106.4603876327229</v>
+        <v>106.817768233445</v>
       </c>
       <c r="I42" t="n">
-        <v>68.80889700235848</v>
+        <v>70.08293774516886</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -25712,16 +25712,16 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>63.03172094509596</v>
+        <v>65.32921403493339</v>
       </c>
       <c r="S42" t="n">
-        <v>160.576284311385</v>
+        <v>161.2636171197674</v>
       </c>
       <c r="T42" t="n">
-        <v>197.7545211476518</v>
+        <v>197.9036731785617</v>
       </c>
       <c r="U42" t="n">
-        <v>225.9020424583333</v>
+        <v>225.9044769310903</v>
       </c>
       <c r="V42" t="n">
         <v>232.8005871494253</v>
@@ -25758,16 +25758,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G43" t="n">
-        <v>167.4896678830489</v>
+        <v>167.5206907817879</v>
       </c>
       <c r="H43" t="n">
-        <v>157.7700577533412</v>
+        <v>158.0458795257661</v>
       </c>
       <c r="I43" t="n">
-        <v>140.3746716485697</v>
+        <v>141.3076148215571</v>
       </c>
       <c r="J43" t="n">
-        <v>57.91645880519738</v>
+        <v>60.10977774604452</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -25788,19 +25788,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>44.1840432516944</v>
+        <v>46.7817879815572</v>
       </c>
       <c r="R43" t="n">
-        <v>154.7526044919236</v>
+        <v>156.1475068297698</v>
       </c>
       <c r="S43" t="n">
-        <v>215.2801062336936</v>
+        <v>215.8207507508087</v>
       </c>
       <c r="T43" t="n">
-        <v>225.8036222151667</v>
+        <v>225.9361746006879</v>
       </c>
       <c r="U43" t="n">
-        <v>286.2916850941958</v>
+        <v>286.2933772523089</v>
       </c>
       <c r="V43" t="n">
         <v>252.137643323828</v>
@@ -25837,13 +25837,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G44" t="n">
-        <v>414.1851495754366</v>
+        <v>414.2543098065221</v>
       </c>
       <c r="H44" t="n">
-        <v>328.02930462833</v>
+        <v>328.737591844935</v>
       </c>
       <c r="I44" t="n">
-        <v>167.3900805251798</v>
+        <v>170.0563803341062</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -25870,16 +25870,16 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>79.66643452406426</v>
+        <v>84.0108208899931</v>
       </c>
       <c r="S44" t="n">
-        <v>183.5530344103659</v>
+        <v>185.1290231762283</v>
       </c>
       <c r="T44" t="n">
-        <v>218.2036083581012</v>
+        <v>218.5063572696783</v>
       </c>
       <c r="U44" t="n">
-        <v>251.2562458726606</v>
+        <v>251.2617786911475</v>
       </c>
       <c r="V44" t="n">
         <v>327.7522584701349</v>
@@ -25916,13 +25916,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G45" t="n">
-        <v>136.7455548990597</v>
+        <v>136.7825588849655</v>
       </c>
       <c r="H45" t="n">
-        <v>106.4603876327229</v>
+        <v>106.817768233445</v>
       </c>
       <c r="I45" t="n">
-        <v>68.80889700235848</v>
+        <v>70.08293774516886</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25949,16 +25949,16 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>63.03172094509596</v>
+        <v>65.32921403493339</v>
       </c>
       <c r="S45" t="n">
-        <v>160.576284311385</v>
+        <v>161.2636171197674</v>
       </c>
       <c r="T45" t="n">
-        <v>197.7545211476518</v>
+        <v>197.9036731785617</v>
       </c>
       <c r="U45" t="n">
-        <v>225.9020424583333</v>
+        <v>225.9044769310903</v>
       </c>
       <c r="V45" t="n">
         <v>232.8005871494253</v>
@@ -25995,16 +25995,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G46" t="n">
-        <v>167.4896678830489</v>
+        <v>167.5206907817879</v>
       </c>
       <c r="H46" t="n">
-        <v>157.7700577533412</v>
+        <v>158.0458795257661</v>
       </c>
       <c r="I46" t="n">
-        <v>140.3746716485697</v>
+        <v>141.3076148215571</v>
       </c>
       <c r="J46" t="n">
-        <v>57.91645880519738</v>
+        <v>60.10977774604452</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -26025,19 +26025,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>44.1840432516944</v>
+        <v>46.7817879815572</v>
       </c>
       <c r="R46" t="n">
-        <v>154.7526044919236</v>
+        <v>156.1475068297698</v>
       </c>
       <c r="S46" t="n">
-        <v>215.2801062336936</v>
+        <v>215.8207507508087</v>
       </c>
       <c r="T46" t="n">
-        <v>225.8036222151667</v>
+        <v>225.9361746006879</v>
       </c>
       <c r="U46" t="n">
-        <v>286.2916850941958</v>
+        <v>286.2933772523089</v>
       </c>
       <c r="V46" t="n">
         <v>252.137643323828</v>
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>363758.3413574412</v>
+        <v>363956.3834967791</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>363758.3413574412</v>
+        <v>363956.3834967791</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>363758.3413574412</v>
+        <v>363956.3834967791</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>363758.3413574412</v>
+        <v>363956.3834967791</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>363758.3413574412</v>
+        <v>363956.3834967791</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>363758.3413574412</v>
+        <v>363956.3834967791</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>363758.3413574412</v>
+        <v>363956.3834967791</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>363758.3413574412</v>
+        <v>363956.3834967791</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>363758.3413574412</v>
+        <v>363956.3834967791</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>363758.3413574412</v>
+        <v>363956.3834967791</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>363758.3413574412</v>
+        <v>363956.3834967791</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>363758.3413574412</v>
+        <v>363956.3834967791</v>
       </c>
     </row>
   </sheetData>
@@ -26270,40 +26270,40 @@
         <v>59129.07304229552</v>
       </c>
       <c r="E2" t="n">
-        <v>64973.66859233286</v>
+        <v>64652.45101500345</v>
       </c>
       <c r="F2" t="n">
-        <v>64973.66859233286</v>
+        <v>64652.45101500345</v>
       </c>
       <c r="G2" t="n">
-        <v>64973.66859233286</v>
+        <v>64652.45101500345</v>
       </c>
       <c r="H2" t="n">
-        <v>64973.66859233286</v>
+        <v>64652.45101500345</v>
       </c>
       <c r="I2" t="n">
-        <v>64973.66859233286</v>
+        <v>64652.45101500345</v>
       </c>
       <c r="J2" t="n">
-        <v>64973.66859233286</v>
+        <v>64652.45101500345</v>
       </c>
       <c r="K2" t="n">
-        <v>64973.66859233285</v>
+        <v>64652.45101500345</v>
       </c>
       <c r="L2" t="n">
-        <v>64973.66859233286</v>
+        <v>64652.45101500345</v>
       </c>
       <c r="M2" t="n">
-        <v>64973.66859233286</v>
+        <v>64652.45101500345</v>
       </c>
       <c r="N2" t="n">
-        <v>64973.66859233286</v>
+        <v>64652.45101500345</v>
       </c>
       <c r="O2" t="n">
-        <v>64973.66859233288</v>
+        <v>64652.45101500345</v>
       </c>
       <c r="P2" t="n">
-        <v>64973.66859233286</v>
+        <v>64652.45101500345</v>
       </c>
     </row>
     <row r="3">
@@ -26322,7 +26322,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>223346.034</v>
+        <v>209524.6041377088</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>48378.33248915087</v>
+        <v>45814.66692941387</v>
       </c>
       <c r="C4" t="n">
-        <v>48378.33248915088</v>
+        <v>45814.66692941387</v>
       </c>
       <c r="D4" t="n">
-        <v>48378.33248915087</v>
+        <v>45814.66692941387</v>
       </c>
       <c r="E4" t="n">
-        <v>15263.20981674642</v>
+        <v>16273.52361464597</v>
       </c>
       <c r="F4" t="n">
-        <v>15263.20981674643</v>
+        <v>16273.52361464597</v>
       </c>
       <c r="G4" t="n">
-        <v>15263.20981674642</v>
+        <v>16273.52361464597</v>
       </c>
       <c r="H4" t="n">
-        <v>15263.20981674643</v>
+        <v>16273.52361464597</v>
       </c>
       <c r="I4" t="n">
-        <v>15263.20981674642</v>
+        <v>16273.52361464597</v>
       </c>
       <c r="J4" t="n">
-        <v>15263.20981674643</v>
+        <v>16273.52361464597</v>
       </c>
       <c r="K4" t="n">
-        <v>15263.20981674642</v>
+        <v>16273.52361464597</v>
       </c>
       <c r="L4" t="n">
-        <v>15263.20981674643</v>
+        <v>16273.52361464597</v>
       </c>
       <c r="M4" t="n">
-        <v>15263.20981674642</v>
+        <v>16273.52361464597</v>
       </c>
       <c r="N4" t="n">
-        <v>15263.20981674643</v>
+        <v>16273.52361464597</v>
       </c>
       <c r="O4" t="n">
-        <v>15263.20981674642</v>
+        <v>16273.52361464597</v>
       </c>
       <c r="P4" t="n">
-        <v>15263.20981674643</v>
+        <v>16273.52361464597</v>
       </c>
     </row>
     <row r="5">
@@ -26426,40 +26426,40 @@
         <v>33627.6</v>
       </c>
       <c r="E5" t="n">
-        <v>6060.399999999999</v>
+        <v>5685.361356880733</v>
       </c>
       <c r="F5" t="n">
-        <v>6060.399999999999</v>
+        <v>5685.361356880733</v>
       </c>
       <c r="G5" t="n">
-        <v>6060.399999999999</v>
+        <v>5685.361356880733</v>
       </c>
       <c r="H5" t="n">
-        <v>6060.399999999999</v>
+        <v>5685.361356880733</v>
       </c>
       <c r="I5" t="n">
-        <v>6060.399999999999</v>
+        <v>5685.361356880733</v>
       </c>
       <c r="J5" t="n">
-        <v>6060.399999999999</v>
+        <v>5685.361356880733</v>
       </c>
       <c r="K5" t="n">
-        <v>6060.399999999999</v>
+        <v>5685.361356880733</v>
       </c>
       <c r="L5" t="n">
-        <v>6060.399999999999</v>
+        <v>5685.361356880733</v>
       </c>
       <c r="M5" t="n">
-        <v>6060.399999999999</v>
+        <v>5685.361356880733</v>
       </c>
       <c r="N5" t="n">
-        <v>6060.399999999999</v>
+        <v>5685.361356880733</v>
       </c>
       <c r="O5" t="n">
-        <v>6060.399999999999</v>
+        <v>5685.361356880733</v>
       </c>
       <c r="P5" t="n">
-        <v>6060.399999999999</v>
+        <v>5685.361356880733</v>
       </c>
     </row>
     <row r="6">
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-22876.85944685536</v>
+        <v>-20313.19388711834</v>
       </c>
       <c r="C6" t="n">
-        <v>-22876.85944685536</v>
+        <v>-20313.19388711834</v>
       </c>
       <c r="D6" t="n">
-        <v>-22876.85944685535</v>
+        <v>-20313.19388711834</v>
       </c>
       <c r="E6" t="n">
-        <v>-179695.9752244135</v>
+        <v>-166831.038094232</v>
       </c>
       <c r="F6" t="n">
-        <v>43650.05877558643</v>
+        <v>42693.56604347675</v>
       </c>
       <c r="G6" t="n">
-        <v>43650.05877558643</v>
+        <v>42693.56604347674</v>
       </c>
       <c r="H6" t="n">
-        <v>43650.05877558643</v>
+        <v>42693.56604347674</v>
       </c>
       <c r="I6" t="n">
-        <v>43650.05877558643</v>
+        <v>42693.56604347674</v>
       </c>
       <c r="J6" t="n">
-        <v>43650.05877558643</v>
+        <v>42693.56604347674</v>
       </c>
       <c r="K6" t="n">
-        <v>43650.05877558642</v>
+        <v>42693.56604347674</v>
       </c>
       <c r="L6" t="n">
-        <v>43650.05877558643</v>
+        <v>42693.56604347674</v>
       </c>
       <c r="M6" t="n">
-        <v>43650.05877558643</v>
+        <v>42693.56604347674</v>
       </c>
       <c r="N6" t="n">
-        <v>43650.05877558643</v>
+        <v>42693.56604347674</v>
       </c>
       <c r="O6" t="n">
-        <v>43650.05877558645</v>
+        <v>42693.56604347675</v>
       </c>
       <c r="P6" t="n">
-        <v>43650.05877558643</v>
+        <v>42693.56604347674</v>
       </c>
     </row>
   </sheetData>
@@ -26684,40 +26684,40 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>277.9999999999999</v>
+        <v>260.7963925174648</v>
       </c>
       <c r="F3" t="n">
-        <v>277.9999999999999</v>
+        <v>260.7963925174648</v>
       </c>
       <c r="G3" t="n">
-        <v>277.9999999999999</v>
+        <v>260.7963925174648</v>
       </c>
       <c r="H3" t="n">
-        <v>277.9999999999999</v>
+        <v>260.7963925174648</v>
       </c>
       <c r="I3" t="n">
-        <v>277.9999999999999</v>
+        <v>260.7963925174648</v>
       </c>
       <c r="J3" t="n">
-        <v>277.9999999999999</v>
+        <v>260.7963925174648</v>
       </c>
       <c r="K3" t="n">
-        <v>277.9999999999999</v>
+        <v>260.7963925174648</v>
       </c>
       <c r="L3" t="n">
-        <v>277.9999999999999</v>
+        <v>260.7963925174648</v>
       </c>
       <c r="M3" t="n">
-        <v>277.9999999999999</v>
+        <v>260.7963925174648</v>
       </c>
       <c r="N3" t="n">
-        <v>277.9999999999999</v>
+        <v>260.7963925174648</v>
       </c>
       <c r="O3" t="n">
-        <v>277.9999999999999</v>
+        <v>260.7963925174648</v>
       </c>
       <c r="P3" t="n">
-        <v>277.9999999999999</v>
+        <v>260.7963925174648</v>
       </c>
     </row>
     <row r="4">
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26901,40 +26901,40 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>278</v>
+        <v>260.7963925174648</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26947,46 +26947,46 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -31670,49 +31670,49 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.117587939698491</v>
+        <v>1.048427708612923</v>
       </c>
       <c r="H11" t="n">
-        <v>11.44549748743718</v>
+        <v>10.7372102708321</v>
       </c>
       <c r="I11" t="n">
-        <v>43.08580904522613</v>
+        <v>40.41950923629976</v>
       </c>
       <c r="J11" t="n">
-        <v>94.85387939698492</v>
+        <v>88.98399123388616</v>
       </c>
       <c r="K11" t="n">
-        <v>142.1613768844221</v>
+        <v>133.3639361394712</v>
       </c>
       <c r="L11" t="n">
-        <v>176.3637587939698</v>
+        <v>165.449755626934</v>
       </c>
       <c r="M11" t="n">
-        <v>196.2386633165829</v>
+        <v>184.0947318899791</v>
       </c>
       <c r="N11" t="n">
-        <v>199.4140100502512</v>
+        <v>187.0735771170756</v>
       </c>
       <c r="O11" t="n">
-        <v>188.3009949748743</v>
+        <v>176.6482740895558</v>
       </c>
       <c r="P11" t="n">
-        <v>160.7105427135678</v>
+        <v>150.7652150331742</v>
       </c>
       <c r="Q11" t="n">
-        <v>120.6869246231155</v>
+        <v>113.2183977184739</v>
       </c>
       <c r="R11" t="n">
-        <v>70.20268341708542</v>
+        <v>65.85829705115658</v>
       </c>
       <c r="S11" t="n">
-        <v>25.4670351758794</v>
+        <v>23.89104641001701</v>
       </c>
       <c r="T11" t="n">
-        <v>4.892241206030149</v>
+        <v>4.589492294453073</v>
       </c>
       <c r="U11" t="n">
-        <v>0.08940703517587929</v>
+        <v>0.08387421668903383</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -31749,22 +31749,22 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5979622641509433</v>
+        <v>0.560958278245113</v>
       </c>
       <c r="H12" t="n">
-        <v>5.775056603773585</v>
+        <v>5.417676003051487</v>
       </c>
       <c r="I12" t="n">
-        <v>20.5877358490566</v>
+        <v>19.31369510624622</v>
       </c>
       <c r="J12" t="n">
-        <v>56.49432075471698</v>
+        <v>52.99825557753501</v>
       </c>
       <c r="K12" t="n">
-        <v>96.55779245283017</v>
+        <v>90.58246021995758</v>
       </c>
       <c r="L12" t="n">
-        <v>129.8338679245283</v>
+        <v>121.799296335633</v>
       </c>
       <c r="M12" t="n">
         <v>142.1340339220183</v>
@@ -31773,25 +31773,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O12" t="n">
-        <v>142.2704339622641</v>
+        <v>133.4662443858011</v>
       </c>
       <c r="P12" t="n">
-        <v>114.1845660377358</v>
+        <v>107.1184277115602</v>
       </c>
       <c r="Q12" t="n">
-        <v>76.32935849056604</v>
+        <v>71.60583214932356</v>
       </c>
       <c r="R12" t="n">
-        <v>37.12611320754718</v>
+        <v>34.82862011770975</v>
       </c>
       <c r="S12" t="n">
-        <v>11.10688679245282</v>
+        <v>10.4195539840704</v>
       </c>
       <c r="T12" t="n">
-        <v>2.41020754716981</v>
+        <v>2.261055516259907</v>
       </c>
       <c r="U12" t="n">
-        <v>0.03933962264150944</v>
+        <v>0.03690514988454693</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -31828,49 +31828,49 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5013114754098359</v>
+        <v>0.4702885766708382</v>
       </c>
       <c r="H13" t="n">
-        <v>4.457114754098362</v>
+        <v>4.181292981673455</v>
       </c>
       <c r="I13" t="n">
-        <v>15.07580327868853</v>
+        <v>14.14286010570121</v>
       </c>
       <c r="J13" t="n">
-        <v>35.4427213114754</v>
+        <v>33.24940237062825</v>
       </c>
       <c r="K13" t="n">
-        <v>58.24327868852456</v>
+        <v>54.63898190775737</v>
       </c>
       <c r="L13" t="n">
-        <v>74.53134426229506</v>
+        <v>69.91908529886263</v>
       </c>
       <c r="M13" t="n">
-        <v>78.58285245901637</v>
+        <v>73.71987206850237</v>
       </c>
       <c r="N13" t="n">
-        <v>76.71432786885249</v>
+        <v>71.96697828272931</v>
       </c>
       <c r="O13" t="n">
-        <v>70.85809836065575</v>
+        <v>66.47315263707449</v>
       </c>
       <c r="P13" t="n">
-        <v>60.63134426229504</v>
+        <v>56.87926567298935</v>
       </c>
       <c r="Q13" t="n">
-        <v>41.97799999999999</v>
+        <v>39.38025527013718</v>
       </c>
       <c r="R13" t="n">
-        <v>22.54078688524589</v>
+        <v>21.14588454739968</v>
       </c>
       <c r="S13" t="n">
-        <v>8.736491803278684</v>
+        <v>8.195847286163604</v>
       </c>
       <c r="T13" t="n">
-        <v>2.141967213114753</v>
+        <v>2.009414827593581</v>
       </c>
       <c r="U13" t="n">
-        <v>0.02734426229508199</v>
+        <v>0.02565210418204575</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -31907,49 +31907,49 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.117587939698491</v>
+        <v>1.048427708612923</v>
       </c>
       <c r="H14" t="n">
-        <v>11.44549748743718</v>
+        <v>10.7372102708321</v>
       </c>
       <c r="I14" t="n">
-        <v>43.08580904522613</v>
+        <v>40.41950923629976</v>
       </c>
       <c r="J14" t="n">
-        <v>94.85387939698492</v>
+        <v>88.98399123388616</v>
       </c>
       <c r="K14" t="n">
-        <v>142.1613768844221</v>
+        <v>133.3639361394712</v>
       </c>
       <c r="L14" t="n">
-        <v>176.3637587939698</v>
+        <v>165.449755626934</v>
       </c>
       <c r="M14" t="n">
-        <v>196.2386633165829</v>
+        <v>184.0947318899791</v>
       </c>
       <c r="N14" t="n">
-        <v>199.4140100502512</v>
+        <v>187.0735771170756</v>
       </c>
       <c r="O14" t="n">
-        <v>188.3009949748743</v>
+        <v>176.6482740895558</v>
       </c>
       <c r="P14" t="n">
-        <v>160.7105427135678</v>
+        <v>150.7652150331742</v>
       </c>
       <c r="Q14" t="n">
-        <v>120.6869246231155</v>
+        <v>113.2183977184739</v>
       </c>
       <c r="R14" t="n">
-        <v>70.20268341708542</v>
+        <v>65.85829705115658</v>
       </c>
       <c r="S14" t="n">
-        <v>25.4670351758794</v>
+        <v>23.89104641001701</v>
       </c>
       <c r="T14" t="n">
-        <v>4.892241206030149</v>
+        <v>4.589492294453073</v>
       </c>
       <c r="U14" t="n">
-        <v>0.08940703517587929</v>
+        <v>0.08387421668903383</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -31986,22 +31986,22 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5979622641509433</v>
+        <v>0.560958278245113</v>
       </c>
       <c r="H15" t="n">
-        <v>5.775056603773585</v>
+        <v>5.417676003051487</v>
       </c>
       <c r="I15" t="n">
-        <v>20.5877358490566</v>
+        <v>19.31369510624622</v>
       </c>
       <c r="J15" t="n">
-        <v>56.49432075471698</v>
+        <v>52.99825557753501</v>
       </c>
       <c r="K15" t="n">
-        <v>96.55779245283017</v>
+        <v>90.58246021995758</v>
       </c>
       <c r="L15" t="n">
-        <v>129.8338679245283</v>
+        <v>121.799296335633</v>
       </c>
       <c r="M15" t="n">
         <v>142.1340339220183</v>
@@ -32010,25 +32010,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O15" t="n">
-        <v>142.2704339622642</v>
+        <v>133.4662443858011</v>
       </c>
       <c r="P15" t="n">
-        <v>114.1845660377358</v>
+        <v>107.1184277115602</v>
       </c>
       <c r="Q15" t="n">
-        <v>76.32935849056604</v>
+        <v>71.60583214932356</v>
       </c>
       <c r="R15" t="n">
-        <v>37.12611320754718</v>
+        <v>34.82862011770975</v>
       </c>
       <c r="S15" t="n">
-        <v>11.10688679245282</v>
+        <v>10.4195539840704</v>
       </c>
       <c r="T15" t="n">
-        <v>2.41020754716981</v>
+        <v>2.261055516259907</v>
       </c>
       <c r="U15" t="n">
-        <v>0.03933962264150944</v>
+        <v>0.03690514988454693</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -32065,49 +32065,49 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5013114754098359</v>
+        <v>0.4702885766708382</v>
       </c>
       <c r="H16" t="n">
-        <v>4.457114754098362</v>
+        <v>4.181292981673455</v>
       </c>
       <c r="I16" t="n">
-        <v>15.07580327868853</v>
+        <v>14.14286010570121</v>
       </c>
       <c r="J16" t="n">
-        <v>35.4427213114754</v>
+        <v>33.24940237062825</v>
       </c>
       <c r="K16" t="n">
-        <v>58.24327868852456</v>
+        <v>54.63898190775737</v>
       </c>
       <c r="L16" t="n">
-        <v>74.53134426229506</v>
+        <v>69.91908529886263</v>
       </c>
       <c r="M16" t="n">
-        <v>78.58285245901637</v>
+        <v>73.71987206850237</v>
       </c>
       <c r="N16" t="n">
-        <v>76.71432786885249</v>
+        <v>71.96697828272931</v>
       </c>
       <c r="O16" t="n">
-        <v>70.85809836065575</v>
+        <v>66.47315263707449</v>
       </c>
       <c r="P16" t="n">
-        <v>60.63134426229504</v>
+        <v>56.87926567298935</v>
       </c>
       <c r="Q16" t="n">
-        <v>41.97799999999999</v>
+        <v>39.38025527013718</v>
       </c>
       <c r="R16" t="n">
-        <v>22.54078688524589</v>
+        <v>21.14588454739968</v>
       </c>
       <c r="S16" t="n">
-        <v>8.736491803278684</v>
+        <v>8.195847286163604</v>
       </c>
       <c r="T16" t="n">
-        <v>2.141967213114753</v>
+        <v>2.009414827593581</v>
       </c>
       <c r="U16" t="n">
-        <v>0.02734426229508199</v>
+        <v>0.02565210418204575</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -32144,49 +32144,49 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.117587939698491</v>
+        <v>1.048427708612923</v>
       </c>
       <c r="H17" t="n">
-        <v>11.44549748743718</v>
+        <v>10.7372102708321</v>
       </c>
       <c r="I17" t="n">
-        <v>43.08580904522613</v>
+        <v>40.41950923629976</v>
       </c>
       <c r="J17" t="n">
-        <v>94.85387939698492</v>
+        <v>88.98399123388617</v>
       </c>
       <c r="K17" t="n">
-        <v>142.1613768844221</v>
+        <v>133.3639361394712</v>
       </c>
       <c r="L17" t="n">
-        <v>176.3637587939698</v>
+        <v>165.449755626934</v>
       </c>
       <c r="M17" t="n">
-        <v>196.2386633165829</v>
+        <v>184.0947318899791</v>
       </c>
       <c r="N17" t="n">
-        <v>199.4140100502512</v>
+        <v>187.0735771170756</v>
       </c>
       <c r="O17" t="n">
-        <v>188.3009949748743</v>
+        <v>176.6482740895558</v>
       </c>
       <c r="P17" t="n">
-        <v>160.7105427135678</v>
+        <v>150.7652150331742</v>
       </c>
       <c r="Q17" t="n">
-        <v>120.6869246231155</v>
+        <v>113.2183977184739</v>
       </c>
       <c r="R17" t="n">
-        <v>70.20268341708542</v>
+        <v>65.8582970511566</v>
       </c>
       <c r="S17" t="n">
-        <v>25.4670351758794</v>
+        <v>23.89104641001701</v>
       </c>
       <c r="T17" t="n">
-        <v>4.892241206030149</v>
+        <v>4.589492294453073</v>
       </c>
       <c r="U17" t="n">
-        <v>0.08940703517587929</v>
+        <v>0.08387421668903385</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -32223,22 +32223,22 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5979622641509433</v>
+        <v>0.560958278245113</v>
       </c>
       <c r="H18" t="n">
-        <v>5.775056603773585</v>
+        <v>5.417676003051488</v>
       </c>
       <c r="I18" t="n">
-        <v>20.5877358490566</v>
+        <v>19.31369510624622</v>
       </c>
       <c r="J18" t="n">
-        <v>56.49432075471698</v>
+        <v>52.99825557753501</v>
       </c>
       <c r="K18" t="n">
-        <v>96.55779245283017</v>
+        <v>90.58246021995758</v>
       </c>
       <c r="L18" t="n">
-        <v>129.8338679245283</v>
+        <v>121.799296335633</v>
       </c>
       <c r="M18" t="n">
         <v>142.1340339220183</v>
@@ -32247,25 +32247,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O18" t="n">
-        <v>142.2704339622641</v>
+        <v>133.4662443858011</v>
       </c>
       <c r="P18" t="n">
-        <v>114.1845660377358</v>
+        <v>107.1184277115602</v>
       </c>
       <c r="Q18" t="n">
-        <v>76.32935849056604</v>
+        <v>71.60583214932356</v>
       </c>
       <c r="R18" t="n">
-        <v>37.12611320754718</v>
+        <v>34.82862011770975</v>
       </c>
       <c r="S18" t="n">
-        <v>11.10688679245282</v>
+        <v>10.41955398407041</v>
       </c>
       <c r="T18" t="n">
-        <v>2.41020754716981</v>
+        <v>2.261055516259907</v>
       </c>
       <c r="U18" t="n">
-        <v>0.03933962264150944</v>
+        <v>0.03690514988454693</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -32302,49 +32302,49 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5013114754098359</v>
+        <v>0.4702885766708382</v>
       </c>
       <c r="H19" t="n">
-        <v>4.457114754098362</v>
+        <v>4.181292981673455</v>
       </c>
       <c r="I19" t="n">
-        <v>15.07580327868853</v>
+        <v>14.14286010570121</v>
       </c>
       <c r="J19" t="n">
-        <v>35.4427213114754</v>
+        <v>33.24940237062826</v>
       </c>
       <c r="K19" t="n">
-        <v>58.24327868852456</v>
+        <v>54.63898190775737</v>
       </c>
       <c r="L19" t="n">
-        <v>74.53134426229506</v>
+        <v>69.91908529886263</v>
       </c>
       <c r="M19" t="n">
-        <v>78.58285245901637</v>
+        <v>73.71987206850237</v>
       </c>
       <c r="N19" t="n">
-        <v>76.71432786885249</v>
+        <v>71.96697828272931</v>
       </c>
       <c r="O19" t="n">
-        <v>70.85809836065575</v>
+        <v>66.47315263707451</v>
       </c>
       <c r="P19" t="n">
-        <v>60.63134426229504</v>
+        <v>56.87926567298936</v>
       </c>
       <c r="Q19" t="n">
-        <v>41.97799999999999</v>
+        <v>39.38025527013719</v>
       </c>
       <c r="R19" t="n">
-        <v>22.54078688524589</v>
+        <v>21.14588454739968</v>
       </c>
       <c r="S19" t="n">
-        <v>8.736491803278684</v>
+        <v>8.195847286163604</v>
       </c>
       <c r="T19" t="n">
-        <v>2.141967213114753</v>
+        <v>2.009414827593581</v>
       </c>
       <c r="U19" t="n">
-        <v>0.02734426229508199</v>
+        <v>0.02565210418204575</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -32381,49 +32381,49 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1.117587939698491</v>
+        <v>1.048427708612923</v>
       </c>
       <c r="H20" t="n">
-        <v>11.44549748743718</v>
+        <v>10.7372102708321</v>
       </c>
       <c r="I20" t="n">
-        <v>43.08580904522613</v>
+        <v>40.41950923629976</v>
       </c>
       <c r="J20" t="n">
-        <v>94.85387939698492</v>
+        <v>88.98399123388616</v>
       </c>
       <c r="K20" t="n">
-        <v>142.1613768844221</v>
+        <v>133.3639361394712</v>
       </c>
       <c r="L20" t="n">
-        <v>176.3637587939698</v>
+        <v>165.449755626934</v>
       </c>
       <c r="M20" t="n">
-        <v>196.2386633165829</v>
+        <v>184.0947318899791</v>
       </c>
       <c r="N20" t="n">
-        <v>199.4140100502512</v>
+        <v>187.0735771170756</v>
       </c>
       <c r="O20" t="n">
-        <v>188.3009949748743</v>
+        <v>176.6482740895558</v>
       </c>
       <c r="P20" t="n">
-        <v>160.7105427135678</v>
+        <v>150.7652150331742</v>
       </c>
       <c r="Q20" t="n">
-        <v>120.6869246231155</v>
+        <v>113.2183977184739</v>
       </c>
       <c r="R20" t="n">
-        <v>70.20268341708542</v>
+        <v>65.85829705115658</v>
       </c>
       <c r="S20" t="n">
-        <v>25.4670351758794</v>
+        <v>23.89104641001701</v>
       </c>
       <c r="T20" t="n">
-        <v>4.892241206030149</v>
+        <v>4.589492294453073</v>
       </c>
       <c r="U20" t="n">
-        <v>0.08940703517587929</v>
+        <v>0.08387421668903383</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -32460,22 +32460,22 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5979622641509433</v>
+        <v>0.560958278245113</v>
       </c>
       <c r="H21" t="n">
-        <v>5.775056603773585</v>
+        <v>5.417676003051487</v>
       </c>
       <c r="I21" t="n">
-        <v>20.5877358490566</v>
+        <v>19.31369510624622</v>
       </c>
       <c r="J21" t="n">
-        <v>56.49432075471698</v>
+        <v>52.99825557753501</v>
       </c>
       <c r="K21" t="n">
-        <v>96.55779245283017</v>
+        <v>90.58246021995758</v>
       </c>
       <c r="L21" t="n">
-        <v>129.8338679245283</v>
+        <v>121.799296335633</v>
       </c>
       <c r="M21" t="n">
         <v>142.1340339220183</v>
@@ -32484,25 +32484,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O21" t="n">
-        <v>142.2704339622641</v>
+        <v>133.4662443858011</v>
       </c>
       <c r="P21" t="n">
-        <v>114.1845660377358</v>
+        <v>107.1184277115602</v>
       </c>
       <c r="Q21" t="n">
-        <v>76.32935849056604</v>
+        <v>71.60583214932356</v>
       </c>
       <c r="R21" t="n">
-        <v>37.12611320754718</v>
+        <v>34.82862011770975</v>
       </c>
       <c r="S21" t="n">
-        <v>11.10688679245282</v>
+        <v>10.4195539840704</v>
       </c>
       <c r="T21" t="n">
-        <v>2.41020754716981</v>
+        <v>2.261055516259907</v>
       </c>
       <c r="U21" t="n">
-        <v>0.03933962264150944</v>
+        <v>0.03690514988454693</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -32539,49 +32539,49 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5013114754098359</v>
+        <v>0.4702885766708382</v>
       </c>
       <c r="H22" t="n">
-        <v>4.457114754098362</v>
+        <v>4.181292981673455</v>
       </c>
       <c r="I22" t="n">
-        <v>15.07580327868853</v>
+        <v>14.14286010570121</v>
       </c>
       <c r="J22" t="n">
-        <v>35.4427213114754</v>
+        <v>33.24940237062825</v>
       </c>
       <c r="K22" t="n">
-        <v>58.24327868852456</v>
+        <v>54.63898190775737</v>
       </c>
       <c r="L22" t="n">
-        <v>74.53134426229506</v>
+        <v>69.91908529886263</v>
       </c>
       <c r="M22" t="n">
-        <v>78.58285245901637</v>
+        <v>73.71987206850237</v>
       </c>
       <c r="N22" t="n">
-        <v>76.71432786885249</v>
+        <v>71.96697828272931</v>
       </c>
       <c r="O22" t="n">
-        <v>70.85809836065575</v>
+        <v>66.47315263707449</v>
       </c>
       <c r="P22" t="n">
-        <v>60.63134426229504</v>
+        <v>56.87926567298935</v>
       </c>
       <c r="Q22" t="n">
-        <v>41.97799999999999</v>
+        <v>39.38025527013718</v>
       </c>
       <c r="R22" t="n">
-        <v>22.54078688524589</v>
+        <v>21.14588454739968</v>
       </c>
       <c r="S22" t="n">
-        <v>8.736491803278684</v>
+        <v>8.195847286163604</v>
       </c>
       <c r="T22" t="n">
-        <v>2.141967213114753</v>
+        <v>2.009414827593581</v>
       </c>
       <c r="U22" t="n">
-        <v>0.02734426229508199</v>
+        <v>0.02565210418204575</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -32618,49 +32618,49 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1.117587939698491</v>
+        <v>1.048427708612923</v>
       </c>
       <c r="H23" t="n">
-        <v>11.44549748743718</v>
+        <v>10.7372102708321</v>
       </c>
       <c r="I23" t="n">
-        <v>43.08580904522613</v>
+        <v>40.41950923629976</v>
       </c>
       <c r="J23" t="n">
-        <v>94.85387939698492</v>
+        <v>88.98399123388616</v>
       </c>
       <c r="K23" t="n">
-        <v>142.1613768844221</v>
+        <v>133.3639361394712</v>
       </c>
       <c r="L23" t="n">
-        <v>176.3637587939698</v>
+        <v>165.449755626934</v>
       </c>
       <c r="M23" t="n">
-        <v>196.2386633165829</v>
+        <v>184.0947318899791</v>
       </c>
       <c r="N23" t="n">
-        <v>199.4140100502512</v>
+        <v>187.0735771170756</v>
       </c>
       <c r="O23" t="n">
-        <v>188.3009949748743</v>
+        <v>176.6482740895558</v>
       </c>
       <c r="P23" t="n">
-        <v>160.7105427135678</v>
+        <v>150.7652150331742</v>
       </c>
       <c r="Q23" t="n">
-        <v>120.6869246231155</v>
+        <v>113.2183977184739</v>
       </c>
       <c r="R23" t="n">
-        <v>70.20268341708542</v>
+        <v>65.85829705115658</v>
       </c>
       <c r="S23" t="n">
-        <v>25.4670351758794</v>
+        <v>23.89104641001701</v>
       </c>
       <c r="T23" t="n">
-        <v>4.892241206030149</v>
+        <v>4.589492294453073</v>
       </c>
       <c r="U23" t="n">
-        <v>0.08940703517587929</v>
+        <v>0.08387421668903383</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -32697,22 +32697,22 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5979622641509433</v>
+        <v>0.560958278245113</v>
       </c>
       <c r="H24" t="n">
-        <v>5.775056603773585</v>
+        <v>5.417676003051487</v>
       </c>
       <c r="I24" t="n">
-        <v>20.5877358490566</v>
+        <v>19.31369510624622</v>
       </c>
       <c r="J24" t="n">
-        <v>56.49432075471698</v>
+        <v>52.99825557753501</v>
       </c>
       <c r="K24" t="n">
-        <v>96.55779245283017</v>
+        <v>90.58246021995758</v>
       </c>
       <c r="L24" t="n">
-        <v>129.8338679245283</v>
+        <v>121.799296335633</v>
       </c>
       <c r="M24" t="n">
         <v>142.1340339220183</v>
@@ -32721,25 +32721,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O24" t="n">
-        <v>142.2704339622642</v>
+        <v>133.4662443858011</v>
       </c>
       <c r="P24" t="n">
-        <v>114.1845660377358</v>
+        <v>107.1184277115602</v>
       </c>
       <c r="Q24" t="n">
-        <v>76.32935849056604</v>
+        <v>71.60583214932356</v>
       </c>
       <c r="R24" t="n">
-        <v>37.12611320754718</v>
+        <v>34.82862011770975</v>
       </c>
       <c r="S24" t="n">
-        <v>11.10688679245282</v>
+        <v>10.4195539840704</v>
       </c>
       <c r="T24" t="n">
-        <v>2.41020754716981</v>
+        <v>2.261055516259907</v>
       </c>
       <c r="U24" t="n">
-        <v>0.03933962264150944</v>
+        <v>0.03690514988454693</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -32776,49 +32776,49 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5013114754098359</v>
+        <v>0.4702885766708382</v>
       </c>
       <c r="H25" t="n">
-        <v>4.457114754098362</v>
+        <v>4.181292981673455</v>
       </c>
       <c r="I25" t="n">
-        <v>15.07580327868853</v>
+        <v>14.14286010570121</v>
       </c>
       <c r="J25" t="n">
-        <v>35.4427213114754</v>
+        <v>33.24940237062825</v>
       </c>
       <c r="K25" t="n">
-        <v>58.24327868852456</v>
+        <v>54.63898190775737</v>
       </c>
       <c r="L25" t="n">
-        <v>74.53134426229506</v>
+        <v>69.91908529886263</v>
       </c>
       <c r="M25" t="n">
-        <v>78.58285245901637</v>
+        <v>73.71987206850237</v>
       </c>
       <c r="N25" t="n">
-        <v>76.71432786885249</v>
+        <v>71.96697828272931</v>
       </c>
       <c r="O25" t="n">
-        <v>70.85809836065575</v>
+        <v>66.47315263707449</v>
       </c>
       <c r="P25" t="n">
-        <v>60.63134426229504</v>
+        <v>56.87926567298935</v>
       </c>
       <c r="Q25" t="n">
-        <v>41.97799999999999</v>
+        <v>39.38025527013718</v>
       </c>
       <c r="R25" t="n">
-        <v>22.54078688524589</v>
+        <v>21.14588454739968</v>
       </c>
       <c r="S25" t="n">
-        <v>8.736491803278684</v>
+        <v>8.195847286163604</v>
       </c>
       <c r="T25" t="n">
-        <v>2.141967213114753</v>
+        <v>2.009414827593581</v>
       </c>
       <c r="U25" t="n">
-        <v>0.02734426229508199</v>
+        <v>0.02565210418204575</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -32855,49 +32855,49 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>1.117587939698491</v>
+        <v>1.048427708612923</v>
       </c>
       <c r="H26" t="n">
-        <v>11.44549748743718</v>
+        <v>10.7372102708321</v>
       </c>
       <c r="I26" t="n">
-        <v>43.08580904522613</v>
+        <v>40.41950923629976</v>
       </c>
       <c r="J26" t="n">
-        <v>94.85387939698492</v>
+        <v>88.98399123388616</v>
       </c>
       <c r="K26" t="n">
-        <v>142.1613768844221</v>
+        <v>133.3639361394712</v>
       </c>
       <c r="L26" t="n">
-        <v>176.3637587939698</v>
+        <v>165.449755626934</v>
       </c>
       <c r="M26" t="n">
-        <v>196.2386633165829</v>
+        <v>184.0947318899791</v>
       </c>
       <c r="N26" t="n">
-        <v>199.4140100502512</v>
+        <v>187.0735771170756</v>
       </c>
       <c r="O26" t="n">
-        <v>188.3009949748743</v>
+        <v>176.6482740895558</v>
       </c>
       <c r="P26" t="n">
-        <v>160.7105427135678</v>
+        <v>150.7652150331742</v>
       </c>
       <c r="Q26" t="n">
-        <v>120.6869246231155</v>
+        <v>113.2183977184739</v>
       </c>
       <c r="R26" t="n">
-        <v>70.20268341708542</v>
+        <v>65.85829705115658</v>
       </c>
       <c r="S26" t="n">
-        <v>25.4670351758794</v>
+        <v>23.89104641001701</v>
       </c>
       <c r="T26" t="n">
-        <v>4.892241206030149</v>
+        <v>4.589492294453073</v>
       </c>
       <c r="U26" t="n">
-        <v>0.08940703517587929</v>
+        <v>0.08387421668903383</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -32934,22 +32934,22 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5979622641509433</v>
+        <v>0.560958278245113</v>
       </c>
       <c r="H27" t="n">
-        <v>5.775056603773585</v>
+        <v>5.417676003051487</v>
       </c>
       <c r="I27" t="n">
-        <v>20.5877358490566</v>
+        <v>19.31369510624622</v>
       </c>
       <c r="J27" t="n">
-        <v>56.49432075471698</v>
+        <v>52.99825557753501</v>
       </c>
       <c r="K27" t="n">
-        <v>96.55779245283017</v>
+        <v>90.58246021995758</v>
       </c>
       <c r="L27" t="n">
-        <v>129.8338679245283</v>
+        <v>121.799296335633</v>
       </c>
       <c r="M27" t="n">
         <v>142.1340339220183</v>
@@ -32958,25 +32958,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O27" t="n">
-        <v>142.2704339622642</v>
+        <v>133.4662443858011</v>
       </c>
       <c r="P27" t="n">
-        <v>114.1845660377358</v>
+        <v>107.1184277115602</v>
       </c>
       <c r="Q27" t="n">
-        <v>76.32935849056604</v>
+        <v>71.60583214932356</v>
       </c>
       <c r="R27" t="n">
-        <v>37.12611320754718</v>
+        <v>34.82862011770975</v>
       </c>
       <c r="S27" t="n">
-        <v>11.10688679245282</v>
+        <v>10.4195539840704</v>
       </c>
       <c r="T27" t="n">
-        <v>2.41020754716981</v>
+        <v>2.261055516259907</v>
       </c>
       <c r="U27" t="n">
-        <v>0.03933962264150944</v>
+        <v>0.03690514988454693</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -33013,49 +33013,49 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5013114754098359</v>
+        <v>0.4702885766708382</v>
       </c>
       <c r="H28" t="n">
-        <v>4.457114754098362</v>
+        <v>4.181292981673455</v>
       </c>
       <c r="I28" t="n">
-        <v>15.07580327868853</v>
+        <v>14.14286010570121</v>
       </c>
       <c r="J28" t="n">
-        <v>35.4427213114754</v>
+        <v>33.24940237062825</v>
       </c>
       <c r="K28" t="n">
-        <v>58.24327868852456</v>
+        <v>54.63898190775737</v>
       </c>
       <c r="L28" t="n">
-        <v>74.53134426229506</v>
+        <v>69.91908529886263</v>
       </c>
       <c r="M28" t="n">
-        <v>78.58285245901637</v>
+        <v>73.71987206850237</v>
       </c>
       <c r="N28" t="n">
-        <v>76.71432786885249</v>
+        <v>71.96697828272931</v>
       </c>
       <c r="O28" t="n">
-        <v>70.85809836065575</v>
+        <v>66.47315263707449</v>
       </c>
       <c r="P28" t="n">
-        <v>60.63134426229504</v>
+        <v>56.87926567298935</v>
       </c>
       <c r="Q28" t="n">
-        <v>41.97799999999999</v>
+        <v>39.38025527013718</v>
       </c>
       <c r="R28" t="n">
-        <v>22.54078688524589</v>
+        <v>21.14588454739968</v>
       </c>
       <c r="S28" t="n">
-        <v>8.736491803278684</v>
+        <v>8.195847286163604</v>
       </c>
       <c r="T28" t="n">
-        <v>2.141967213114753</v>
+        <v>2.009414827593581</v>
       </c>
       <c r="U28" t="n">
-        <v>0.02734426229508199</v>
+        <v>0.02565210418204575</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -33092,49 +33092,49 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>1.117587939698491</v>
+        <v>1.048427708612923</v>
       </c>
       <c r="H29" t="n">
-        <v>11.44549748743718</v>
+        <v>10.7372102708321</v>
       </c>
       <c r="I29" t="n">
-        <v>43.08580904522613</v>
+        <v>40.41950923629976</v>
       </c>
       <c r="J29" t="n">
-        <v>94.85387939698492</v>
+        <v>88.98399123388616</v>
       </c>
       <c r="K29" t="n">
-        <v>142.1613768844221</v>
+        <v>133.3639361394712</v>
       </c>
       <c r="L29" t="n">
-        <v>176.3637587939698</v>
+        <v>165.449755626934</v>
       </c>
       <c r="M29" t="n">
-        <v>196.2386633165829</v>
+        <v>184.0947318899791</v>
       </c>
       <c r="N29" t="n">
-        <v>199.4140100502512</v>
+        <v>187.0735771170756</v>
       </c>
       <c r="O29" t="n">
-        <v>188.3009949748743</v>
+        <v>176.6482740895558</v>
       </c>
       <c r="P29" t="n">
-        <v>160.7105427135678</v>
+        <v>150.7652150331742</v>
       </c>
       <c r="Q29" t="n">
-        <v>120.6869246231155</v>
+        <v>113.2183977184739</v>
       </c>
       <c r="R29" t="n">
-        <v>70.20268341708542</v>
+        <v>65.85829705115658</v>
       </c>
       <c r="S29" t="n">
-        <v>25.4670351758794</v>
+        <v>23.89104641001701</v>
       </c>
       <c r="T29" t="n">
-        <v>4.892241206030149</v>
+        <v>4.589492294453073</v>
       </c>
       <c r="U29" t="n">
-        <v>0.08940703517587929</v>
+        <v>0.08387421668903383</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -33171,22 +33171,22 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5979622641509433</v>
+        <v>0.560958278245113</v>
       </c>
       <c r="H30" t="n">
-        <v>5.775056603773585</v>
+        <v>5.417676003051487</v>
       </c>
       <c r="I30" t="n">
-        <v>20.5877358490566</v>
+        <v>19.31369510624622</v>
       </c>
       <c r="J30" t="n">
-        <v>56.49432075471698</v>
+        <v>52.99825557753501</v>
       </c>
       <c r="K30" t="n">
-        <v>96.55779245283017</v>
+        <v>90.58246021995758</v>
       </c>
       <c r="L30" t="n">
-        <v>129.8338679245283</v>
+        <v>121.799296335633</v>
       </c>
       <c r="M30" t="n">
         <v>142.1340339220183</v>
@@ -33195,25 +33195,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O30" t="n">
-        <v>142.2704339622641</v>
+        <v>133.4662443858011</v>
       </c>
       <c r="P30" t="n">
-        <v>114.1845660377358</v>
+        <v>107.1184277115602</v>
       </c>
       <c r="Q30" t="n">
-        <v>76.32935849056604</v>
+        <v>71.60583214932356</v>
       </c>
       <c r="R30" t="n">
-        <v>37.12611320754718</v>
+        <v>34.82862011770975</v>
       </c>
       <c r="S30" t="n">
-        <v>11.10688679245282</v>
+        <v>10.4195539840704</v>
       </c>
       <c r="T30" t="n">
-        <v>2.41020754716981</v>
+        <v>2.261055516259907</v>
       </c>
       <c r="U30" t="n">
-        <v>0.03933962264150944</v>
+        <v>0.03690514988454693</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -33250,49 +33250,49 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5013114754098359</v>
+        <v>0.4702885766708382</v>
       </c>
       <c r="H31" t="n">
-        <v>4.457114754098362</v>
+        <v>4.181292981673455</v>
       </c>
       <c r="I31" t="n">
-        <v>15.07580327868853</v>
+        <v>14.14286010570121</v>
       </c>
       <c r="J31" t="n">
-        <v>35.4427213114754</v>
+        <v>33.24940237062825</v>
       </c>
       <c r="K31" t="n">
-        <v>58.24327868852456</v>
+        <v>54.63898190775737</v>
       </c>
       <c r="L31" t="n">
-        <v>74.53134426229506</v>
+        <v>69.91908529886263</v>
       </c>
       <c r="M31" t="n">
-        <v>78.58285245901637</v>
+        <v>73.71987206850237</v>
       </c>
       <c r="N31" t="n">
-        <v>76.71432786885249</v>
+        <v>71.96697828272931</v>
       </c>
       <c r="O31" t="n">
-        <v>70.85809836065575</v>
+        <v>66.47315263707449</v>
       </c>
       <c r="P31" t="n">
-        <v>60.63134426229504</v>
+        <v>56.87926567298935</v>
       </c>
       <c r="Q31" t="n">
-        <v>41.97799999999999</v>
+        <v>39.38025527013718</v>
       </c>
       <c r="R31" t="n">
-        <v>22.54078688524589</v>
+        <v>21.14588454739968</v>
       </c>
       <c r="S31" t="n">
-        <v>8.736491803278684</v>
+        <v>8.195847286163604</v>
       </c>
       <c r="T31" t="n">
-        <v>2.141967213114753</v>
+        <v>2.009414827593581</v>
       </c>
       <c r="U31" t="n">
-        <v>0.02734426229508199</v>
+        <v>0.02565210418204575</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -33329,49 +33329,49 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1.117587939698491</v>
+        <v>1.048427708612923</v>
       </c>
       <c r="H32" t="n">
-        <v>11.44549748743718</v>
+        <v>10.7372102708321</v>
       </c>
       <c r="I32" t="n">
-        <v>43.08580904522613</v>
+        <v>40.41950923629976</v>
       </c>
       <c r="J32" t="n">
-        <v>94.85387939698492</v>
+        <v>88.98399123388616</v>
       </c>
       <c r="K32" t="n">
-        <v>142.1613768844221</v>
+        <v>133.3639361394712</v>
       </c>
       <c r="L32" t="n">
-        <v>176.3637587939698</v>
+        <v>165.449755626934</v>
       </c>
       <c r="M32" t="n">
-        <v>196.2386633165829</v>
+        <v>184.0947318899791</v>
       </c>
       <c r="N32" t="n">
-        <v>199.4140100502512</v>
+        <v>187.0735771170756</v>
       </c>
       <c r="O32" t="n">
-        <v>188.3009949748743</v>
+        <v>176.6482740895558</v>
       </c>
       <c r="P32" t="n">
-        <v>160.7105427135678</v>
+        <v>150.7652150331742</v>
       </c>
       <c r="Q32" t="n">
-        <v>120.6869246231155</v>
+        <v>113.2183977184739</v>
       </c>
       <c r="R32" t="n">
-        <v>70.20268341708542</v>
+        <v>65.85829705115658</v>
       </c>
       <c r="S32" t="n">
-        <v>25.4670351758794</v>
+        <v>23.89104641001701</v>
       </c>
       <c r="T32" t="n">
-        <v>4.892241206030149</v>
+        <v>4.589492294453073</v>
       </c>
       <c r="U32" t="n">
-        <v>0.08940703517587929</v>
+        <v>0.08387421668903383</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -33408,22 +33408,22 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.5979622641509433</v>
+        <v>0.560958278245113</v>
       </c>
       <c r="H33" t="n">
-        <v>5.775056603773585</v>
+        <v>5.417676003051487</v>
       </c>
       <c r="I33" t="n">
-        <v>20.5877358490566</v>
+        <v>19.31369510624622</v>
       </c>
       <c r="J33" t="n">
-        <v>56.49432075471698</v>
+        <v>52.99825557753501</v>
       </c>
       <c r="K33" t="n">
-        <v>96.55779245283017</v>
+        <v>90.58246021995758</v>
       </c>
       <c r="L33" t="n">
-        <v>129.8338679245283</v>
+        <v>121.799296335633</v>
       </c>
       <c r="M33" t="n">
         <v>142.1340339220183</v>
@@ -33432,25 +33432,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O33" t="n">
-        <v>142.2704339622641</v>
+        <v>133.4662443858011</v>
       </c>
       <c r="P33" t="n">
-        <v>114.1845660377358</v>
+        <v>107.1184277115602</v>
       </c>
       <c r="Q33" t="n">
-        <v>76.32935849056604</v>
+        <v>71.60583214932356</v>
       </c>
       <c r="R33" t="n">
-        <v>37.12611320754718</v>
+        <v>34.82862011770975</v>
       </c>
       <c r="S33" t="n">
-        <v>11.10688679245282</v>
+        <v>10.4195539840704</v>
       </c>
       <c r="T33" t="n">
-        <v>2.41020754716981</v>
+        <v>2.261055516259907</v>
       </c>
       <c r="U33" t="n">
-        <v>0.03933962264150944</v>
+        <v>0.03690514988454693</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -33487,49 +33487,49 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5013114754098359</v>
+        <v>0.4702885766708382</v>
       </c>
       <c r="H34" t="n">
-        <v>4.457114754098362</v>
+        <v>4.181292981673455</v>
       </c>
       <c r="I34" t="n">
-        <v>15.07580327868853</v>
+        <v>14.14286010570121</v>
       </c>
       <c r="J34" t="n">
-        <v>35.4427213114754</v>
+        <v>33.24940237062825</v>
       </c>
       <c r="K34" t="n">
-        <v>58.24327868852456</v>
+        <v>54.63898190775737</v>
       </c>
       <c r="L34" t="n">
-        <v>74.53134426229506</v>
+        <v>69.91908529886263</v>
       </c>
       <c r="M34" t="n">
-        <v>78.58285245901637</v>
+        <v>73.71987206850237</v>
       </c>
       <c r="N34" t="n">
-        <v>76.71432786885249</v>
+        <v>71.96697828272931</v>
       </c>
       <c r="O34" t="n">
-        <v>70.85809836065575</v>
+        <v>66.47315263707449</v>
       </c>
       <c r="P34" t="n">
-        <v>60.63134426229504</v>
+        <v>56.87926567298935</v>
       </c>
       <c r="Q34" t="n">
-        <v>41.97799999999999</v>
+        <v>39.38025527013718</v>
       </c>
       <c r="R34" t="n">
-        <v>22.54078688524589</v>
+        <v>21.14588454739968</v>
       </c>
       <c r="S34" t="n">
-        <v>8.736491803278684</v>
+        <v>8.195847286163604</v>
       </c>
       <c r="T34" t="n">
-        <v>2.141967213114753</v>
+        <v>2.009414827593581</v>
       </c>
       <c r="U34" t="n">
-        <v>0.02734426229508199</v>
+        <v>0.02565210418204575</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -33566,49 +33566,49 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>1.117587939698491</v>
+        <v>1.048427708612923</v>
       </c>
       <c r="H35" t="n">
-        <v>11.44549748743718</v>
+        <v>10.7372102708321</v>
       </c>
       <c r="I35" t="n">
-        <v>43.08580904522613</v>
+        <v>40.41950923629976</v>
       </c>
       <c r="J35" t="n">
-        <v>94.85387939698492</v>
+        <v>88.98399123388616</v>
       </c>
       <c r="K35" t="n">
-        <v>142.1613768844221</v>
+        <v>133.3639361394712</v>
       </c>
       <c r="L35" t="n">
-        <v>176.3637587939698</v>
+        <v>165.449755626934</v>
       </c>
       <c r="M35" t="n">
-        <v>196.2386633165829</v>
+        <v>184.0947318899791</v>
       </c>
       <c r="N35" t="n">
-        <v>199.4140100502512</v>
+        <v>187.0735771170756</v>
       </c>
       <c r="O35" t="n">
-        <v>188.3009949748743</v>
+        <v>176.6482740895558</v>
       </c>
       <c r="P35" t="n">
-        <v>160.7105427135678</v>
+        <v>150.7652150331742</v>
       </c>
       <c r="Q35" t="n">
-        <v>120.6869246231155</v>
+        <v>113.2183977184739</v>
       </c>
       <c r="R35" t="n">
-        <v>70.20268341708542</v>
+        <v>65.85829705115658</v>
       </c>
       <c r="S35" t="n">
-        <v>25.4670351758794</v>
+        <v>23.89104641001701</v>
       </c>
       <c r="T35" t="n">
-        <v>4.892241206030149</v>
+        <v>4.589492294453073</v>
       </c>
       <c r="U35" t="n">
-        <v>0.08940703517587929</v>
+        <v>0.08387421668903383</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -33645,22 +33645,22 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.5979622641509433</v>
+        <v>0.560958278245113</v>
       </c>
       <c r="H36" t="n">
-        <v>5.775056603773585</v>
+        <v>5.417676003051487</v>
       </c>
       <c r="I36" t="n">
-        <v>20.5877358490566</v>
+        <v>19.31369510624622</v>
       </c>
       <c r="J36" t="n">
-        <v>56.49432075471698</v>
+        <v>52.99825557753501</v>
       </c>
       <c r="K36" t="n">
-        <v>96.55779245283017</v>
+        <v>90.58246021995758</v>
       </c>
       <c r="L36" t="n">
-        <v>129.8338679245283</v>
+        <v>121.799296335633</v>
       </c>
       <c r="M36" t="n">
         <v>142.1340339220183</v>
@@ -33669,25 +33669,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O36" t="n">
-        <v>142.2704339622641</v>
+        <v>133.4662443858011</v>
       </c>
       <c r="P36" t="n">
-        <v>114.1845660377358</v>
+        <v>107.1184277115602</v>
       </c>
       <c r="Q36" t="n">
-        <v>76.32935849056604</v>
+        <v>71.60583214932356</v>
       </c>
       <c r="R36" t="n">
-        <v>37.12611320754718</v>
+        <v>34.82862011770975</v>
       </c>
       <c r="S36" t="n">
-        <v>11.10688679245282</v>
+        <v>10.4195539840704</v>
       </c>
       <c r="T36" t="n">
-        <v>2.41020754716981</v>
+        <v>2.261055516259907</v>
       </c>
       <c r="U36" t="n">
-        <v>0.03933962264150944</v>
+        <v>0.03690514988454693</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -33724,49 +33724,49 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.5013114754098359</v>
+        <v>0.4702885766708382</v>
       </c>
       <c r="H37" t="n">
-        <v>4.457114754098362</v>
+        <v>4.181292981673455</v>
       </c>
       <c r="I37" t="n">
-        <v>15.07580327868853</v>
+        <v>14.14286010570121</v>
       </c>
       <c r="J37" t="n">
-        <v>35.4427213114754</v>
+        <v>33.24940237062825</v>
       </c>
       <c r="K37" t="n">
-        <v>58.24327868852456</v>
+        <v>54.63898190775737</v>
       </c>
       <c r="L37" t="n">
-        <v>74.53134426229506</v>
+        <v>69.91908529886263</v>
       </c>
       <c r="M37" t="n">
-        <v>78.58285245901637</v>
+        <v>73.71987206850237</v>
       </c>
       <c r="N37" t="n">
-        <v>76.71432786885249</v>
+        <v>71.96697828272931</v>
       </c>
       <c r="O37" t="n">
-        <v>70.85809836065575</v>
+        <v>66.47315263707449</v>
       </c>
       <c r="P37" t="n">
-        <v>60.63134426229504</v>
+        <v>56.87926567298935</v>
       </c>
       <c r="Q37" t="n">
-        <v>41.97799999999999</v>
+        <v>39.38025527013718</v>
       </c>
       <c r="R37" t="n">
-        <v>22.54078688524589</v>
+        <v>21.14588454739968</v>
       </c>
       <c r="S37" t="n">
-        <v>8.736491803278684</v>
+        <v>8.195847286163604</v>
       </c>
       <c r="T37" t="n">
-        <v>2.141967213114753</v>
+        <v>2.009414827593581</v>
       </c>
       <c r="U37" t="n">
-        <v>0.02734426229508199</v>
+        <v>0.02565210418204575</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -33803,49 +33803,49 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1.117587939698491</v>
+        <v>1.048427708612923</v>
       </c>
       <c r="H38" t="n">
-        <v>11.44549748743718</v>
+        <v>10.7372102708321</v>
       </c>
       <c r="I38" t="n">
-        <v>43.08580904522613</v>
+        <v>40.41950923629976</v>
       </c>
       <c r="J38" t="n">
-        <v>94.85387939698492</v>
+        <v>88.98399123388616</v>
       </c>
       <c r="K38" t="n">
-        <v>142.1613768844221</v>
+        <v>133.3639361394712</v>
       </c>
       <c r="L38" t="n">
-        <v>176.3637587939698</v>
+        <v>165.449755626934</v>
       </c>
       <c r="M38" t="n">
-        <v>196.2386633165829</v>
+        <v>184.0947318899791</v>
       </c>
       <c r="N38" t="n">
-        <v>199.4140100502512</v>
+        <v>187.0735771170756</v>
       </c>
       <c r="O38" t="n">
-        <v>188.3009949748743</v>
+        <v>176.6482740895558</v>
       </c>
       <c r="P38" t="n">
-        <v>160.7105427135678</v>
+        <v>150.7652150331742</v>
       </c>
       <c r="Q38" t="n">
-        <v>120.6869246231155</v>
+        <v>113.2183977184739</v>
       </c>
       <c r="R38" t="n">
-        <v>70.20268341708542</v>
+        <v>65.85829705115658</v>
       </c>
       <c r="S38" t="n">
-        <v>25.4670351758794</v>
+        <v>23.89104641001701</v>
       </c>
       <c r="T38" t="n">
-        <v>4.892241206030149</v>
+        <v>4.589492294453073</v>
       </c>
       <c r="U38" t="n">
-        <v>0.08940703517587929</v>
+        <v>0.08387421668903383</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -33882,22 +33882,22 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.5979622641509433</v>
+        <v>0.560958278245113</v>
       </c>
       <c r="H39" t="n">
-        <v>5.775056603773585</v>
+        <v>5.417676003051487</v>
       </c>
       <c r="I39" t="n">
-        <v>20.5877358490566</v>
+        <v>19.31369510624622</v>
       </c>
       <c r="J39" t="n">
-        <v>56.49432075471698</v>
+        <v>52.99825557753501</v>
       </c>
       <c r="K39" t="n">
-        <v>96.55779245283017</v>
+        <v>90.58246021995758</v>
       </c>
       <c r="L39" t="n">
-        <v>129.8338679245283</v>
+        <v>121.799296335633</v>
       </c>
       <c r="M39" t="n">
         <v>142.1340339220183</v>
@@ -33906,25 +33906,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O39" t="n">
-        <v>142.2704339622641</v>
+        <v>133.4662443858011</v>
       </c>
       <c r="P39" t="n">
-        <v>114.1845660377358</v>
+        <v>107.1184277115602</v>
       </c>
       <c r="Q39" t="n">
-        <v>76.32935849056604</v>
+        <v>71.60583214932356</v>
       </c>
       <c r="R39" t="n">
-        <v>37.12611320754718</v>
+        <v>34.82862011770975</v>
       </c>
       <c r="S39" t="n">
-        <v>11.10688679245282</v>
+        <v>10.4195539840704</v>
       </c>
       <c r="T39" t="n">
-        <v>2.41020754716981</v>
+        <v>2.261055516259907</v>
       </c>
       <c r="U39" t="n">
-        <v>0.03933962264150944</v>
+        <v>0.03690514988454693</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -33961,49 +33961,49 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.5013114754098359</v>
+        <v>0.4702885766708382</v>
       </c>
       <c r="H40" t="n">
-        <v>4.457114754098362</v>
+        <v>4.181292981673455</v>
       </c>
       <c r="I40" t="n">
-        <v>15.07580327868853</v>
+        <v>14.14286010570121</v>
       </c>
       <c r="J40" t="n">
-        <v>35.4427213114754</v>
+        <v>33.24940237062825</v>
       </c>
       <c r="K40" t="n">
-        <v>58.24327868852456</v>
+        <v>54.63898190775737</v>
       </c>
       <c r="L40" t="n">
-        <v>74.53134426229506</v>
+        <v>69.91908529886263</v>
       </c>
       <c r="M40" t="n">
-        <v>78.58285245901637</v>
+        <v>73.71987206850237</v>
       </c>
       <c r="N40" t="n">
-        <v>76.71432786885249</v>
+        <v>71.96697828272931</v>
       </c>
       <c r="O40" t="n">
-        <v>70.85809836065575</v>
+        <v>66.47315263707449</v>
       </c>
       <c r="P40" t="n">
-        <v>60.63134426229504</v>
+        <v>56.87926567298935</v>
       </c>
       <c r="Q40" t="n">
-        <v>41.97799999999999</v>
+        <v>39.38025527013718</v>
       </c>
       <c r="R40" t="n">
-        <v>22.54078688524589</v>
+        <v>21.14588454739968</v>
       </c>
       <c r="S40" t="n">
-        <v>8.736491803278684</v>
+        <v>8.195847286163604</v>
       </c>
       <c r="T40" t="n">
-        <v>2.141967213114753</v>
+        <v>2.009414827593581</v>
       </c>
       <c r="U40" t="n">
-        <v>0.02734426229508199</v>
+        <v>0.02565210418204575</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -34040,49 +34040,49 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>1.117587939698491</v>
+        <v>1.048427708612923</v>
       </c>
       <c r="H41" t="n">
-        <v>11.44549748743718</v>
+        <v>10.7372102708321</v>
       </c>
       <c r="I41" t="n">
-        <v>43.08580904522613</v>
+        <v>40.41950923629976</v>
       </c>
       <c r="J41" t="n">
-        <v>94.85387939698492</v>
+        <v>88.98399123388616</v>
       </c>
       <c r="K41" t="n">
-        <v>142.1613768844221</v>
+        <v>133.3639361394712</v>
       </c>
       <c r="L41" t="n">
-        <v>176.3637587939698</v>
+        <v>165.449755626934</v>
       </c>
       <c r="M41" t="n">
-        <v>196.2386633165829</v>
+        <v>184.0947318899791</v>
       </c>
       <c r="N41" t="n">
-        <v>199.4140100502512</v>
+        <v>187.0735771170756</v>
       </c>
       <c r="O41" t="n">
-        <v>188.3009949748743</v>
+        <v>176.6482740895558</v>
       </c>
       <c r="P41" t="n">
-        <v>160.7105427135678</v>
+        <v>150.7652150331742</v>
       </c>
       <c r="Q41" t="n">
-        <v>120.6869246231155</v>
+        <v>113.2183977184739</v>
       </c>
       <c r="R41" t="n">
-        <v>70.20268341708542</v>
+        <v>65.85829705115658</v>
       </c>
       <c r="S41" t="n">
-        <v>25.4670351758794</v>
+        <v>23.89104641001701</v>
       </c>
       <c r="T41" t="n">
-        <v>4.892241206030149</v>
+        <v>4.589492294453073</v>
       </c>
       <c r="U41" t="n">
-        <v>0.08940703517587929</v>
+        <v>0.08387421668903383</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -34119,22 +34119,22 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.5979622641509433</v>
+        <v>0.560958278245113</v>
       </c>
       <c r="H42" t="n">
-        <v>5.775056603773585</v>
+        <v>5.417676003051487</v>
       </c>
       <c r="I42" t="n">
-        <v>20.5877358490566</v>
+        <v>19.31369510624622</v>
       </c>
       <c r="J42" t="n">
-        <v>56.49432075471698</v>
+        <v>52.99825557753501</v>
       </c>
       <c r="K42" t="n">
-        <v>96.55779245283017</v>
+        <v>90.58246021995758</v>
       </c>
       <c r="L42" t="n">
-        <v>129.8338679245283</v>
+        <v>121.799296335633</v>
       </c>
       <c r="M42" t="n">
         <v>142.1340339220183</v>
@@ -34143,25 +34143,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O42" t="n">
-        <v>142.2704339622641</v>
+        <v>133.4662443858011</v>
       </c>
       <c r="P42" t="n">
-        <v>114.1845660377358</v>
+        <v>107.1184277115602</v>
       </c>
       <c r="Q42" t="n">
-        <v>76.32935849056604</v>
+        <v>71.60583214932356</v>
       </c>
       <c r="R42" t="n">
-        <v>37.12611320754718</v>
+        <v>34.82862011770975</v>
       </c>
       <c r="S42" t="n">
-        <v>11.10688679245282</v>
+        <v>10.4195539840704</v>
       </c>
       <c r="T42" t="n">
-        <v>2.41020754716981</v>
+        <v>2.261055516259907</v>
       </c>
       <c r="U42" t="n">
-        <v>0.03933962264150944</v>
+        <v>0.03690514988454693</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -34198,49 +34198,49 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.5013114754098359</v>
+        <v>0.4702885766708382</v>
       </c>
       <c r="H43" t="n">
-        <v>4.457114754098362</v>
+        <v>4.181292981673455</v>
       </c>
       <c r="I43" t="n">
-        <v>15.07580327868853</v>
+        <v>14.14286010570121</v>
       </c>
       <c r="J43" t="n">
-        <v>35.4427213114754</v>
+        <v>33.24940237062825</v>
       </c>
       <c r="K43" t="n">
-        <v>58.24327868852456</v>
+        <v>54.63898190775737</v>
       </c>
       <c r="L43" t="n">
-        <v>74.53134426229506</v>
+        <v>69.91908529886263</v>
       </c>
       <c r="M43" t="n">
-        <v>78.58285245901637</v>
+        <v>73.71987206850237</v>
       </c>
       <c r="N43" t="n">
-        <v>76.71432786885249</v>
+        <v>71.96697828272931</v>
       </c>
       <c r="O43" t="n">
-        <v>70.85809836065575</v>
+        <v>66.47315263707449</v>
       </c>
       <c r="P43" t="n">
-        <v>60.63134426229504</v>
+        <v>56.87926567298935</v>
       </c>
       <c r="Q43" t="n">
-        <v>41.97799999999999</v>
+        <v>39.38025527013718</v>
       </c>
       <c r="R43" t="n">
-        <v>22.54078688524589</v>
+        <v>21.14588454739968</v>
       </c>
       <c r="S43" t="n">
-        <v>8.736491803278684</v>
+        <v>8.195847286163604</v>
       </c>
       <c r="T43" t="n">
-        <v>2.141967213114753</v>
+        <v>2.009414827593581</v>
       </c>
       <c r="U43" t="n">
-        <v>0.02734426229508199</v>
+        <v>0.02565210418204575</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -34277,49 +34277,49 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>1.117587939698491</v>
+        <v>1.048427708612923</v>
       </c>
       <c r="H44" t="n">
-        <v>11.44549748743718</v>
+        <v>10.7372102708321</v>
       </c>
       <c r="I44" t="n">
-        <v>43.08580904522613</v>
+        <v>40.41950923629976</v>
       </c>
       <c r="J44" t="n">
-        <v>94.85387939698492</v>
+        <v>88.98399123388616</v>
       </c>
       <c r="K44" t="n">
-        <v>142.1613768844221</v>
+        <v>133.3639361394712</v>
       </c>
       <c r="L44" t="n">
-        <v>176.3637587939698</v>
+        <v>165.449755626934</v>
       </c>
       <c r="M44" t="n">
-        <v>196.2386633165829</v>
+        <v>184.0947318899791</v>
       </c>
       <c r="N44" t="n">
-        <v>199.4140100502512</v>
+        <v>187.0735771170756</v>
       </c>
       <c r="O44" t="n">
-        <v>188.3009949748743</v>
+        <v>176.6482740895558</v>
       </c>
       <c r="P44" t="n">
-        <v>160.7105427135678</v>
+        <v>150.7652150331742</v>
       </c>
       <c r="Q44" t="n">
-        <v>120.6869246231155</v>
+        <v>113.2183977184739</v>
       </c>
       <c r="R44" t="n">
-        <v>70.20268341708542</v>
+        <v>65.85829705115658</v>
       </c>
       <c r="S44" t="n">
-        <v>25.4670351758794</v>
+        <v>23.89104641001701</v>
       </c>
       <c r="T44" t="n">
-        <v>4.892241206030149</v>
+        <v>4.589492294453073</v>
       </c>
       <c r="U44" t="n">
-        <v>0.08940703517587929</v>
+        <v>0.08387421668903383</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -34356,22 +34356,22 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.5979622641509433</v>
+        <v>0.560958278245113</v>
       </c>
       <c r="H45" t="n">
-        <v>5.775056603773585</v>
+        <v>5.417676003051487</v>
       </c>
       <c r="I45" t="n">
-        <v>20.5877358490566</v>
+        <v>19.31369510624622</v>
       </c>
       <c r="J45" t="n">
-        <v>56.49432075471698</v>
+        <v>52.99825557753501</v>
       </c>
       <c r="K45" t="n">
-        <v>96.55779245283017</v>
+        <v>90.58246021995758</v>
       </c>
       <c r="L45" t="n">
-        <v>129.8338679245283</v>
+        <v>121.799296335633</v>
       </c>
       <c r="M45" t="n">
         <v>142.1340339220183</v>
@@ -34380,25 +34380,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O45" t="n">
-        <v>142.2704339622641</v>
+        <v>133.4662443858011</v>
       </c>
       <c r="P45" t="n">
-        <v>114.1845660377358</v>
+        <v>107.1184277115602</v>
       </c>
       <c r="Q45" t="n">
-        <v>76.32935849056604</v>
+        <v>71.60583214932356</v>
       </c>
       <c r="R45" t="n">
-        <v>37.12611320754718</v>
+        <v>34.82862011770975</v>
       </c>
       <c r="S45" t="n">
-        <v>11.10688679245282</v>
+        <v>10.4195539840704</v>
       </c>
       <c r="T45" t="n">
-        <v>2.41020754716981</v>
+        <v>2.261055516259907</v>
       </c>
       <c r="U45" t="n">
-        <v>0.03933962264150944</v>
+        <v>0.03690514988454693</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -34435,49 +34435,49 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.5013114754098359</v>
+        <v>0.4702885766708382</v>
       </c>
       <c r="H46" t="n">
-        <v>4.457114754098362</v>
+        <v>4.181292981673455</v>
       </c>
       <c r="I46" t="n">
-        <v>15.07580327868853</v>
+        <v>14.14286010570121</v>
       </c>
       <c r="J46" t="n">
-        <v>35.4427213114754</v>
+        <v>33.24940237062825</v>
       </c>
       <c r="K46" t="n">
-        <v>58.24327868852456</v>
+        <v>54.63898190775737</v>
       </c>
       <c r="L46" t="n">
-        <v>74.53134426229506</v>
+        <v>69.91908529886263</v>
       </c>
       <c r="M46" t="n">
-        <v>78.58285245901637</v>
+        <v>73.71987206850237</v>
       </c>
       <c r="N46" t="n">
-        <v>76.71432786885249</v>
+        <v>71.96697828272931</v>
       </c>
       <c r="O46" t="n">
-        <v>70.85809836065575</v>
+        <v>66.47315263707449</v>
       </c>
       <c r="P46" t="n">
-        <v>60.63134426229504</v>
+        <v>56.87926567298935</v>
       </c>
       <c r="Q46" t="n">
-        <v>41.97799999999999</v>
+        <v>39.38025527013718</v>
       </c>
       <c r="R46" t="n">
-        <v>22.54078688524589</v>
+        <v>21.14588454739968</v>
       </c>
       <c r="S46" t="n">
-        <v>8.736491803278684</v>
+        <v>8.195847286163604</v>
       </c>
       <c r="T46" t="n">
-        <v>2.141967213114753</v>
+        <v>2.009414827593581</v>
       </c>
       <c r="U46" t="n">
-        <v>0.02734426229508199</v>
+        <v>0.02565210418204575</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
